--- a/research/traditional_assets/database/data/serbia/serbia_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/serbia/serbia_chemical_specialty.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1238685724401964</v>
+        <v>0.1237210195815361</v>
       </c>
       <c r="C2">
-        <v>326.1076570240353</v>
+        <v>323.1515851773899</v>
       </c>
       <c r="D2">
-        <v>276.5076570240353</v>
+        <v>276.8126551773899</v>
       </c>
       <c r="E2">
-        <v>-0.006999999999999999</v>
+        <v>3.25407</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.26107</v>
       </c>
       <c r="G2">
         <v>49.6</v>
@@ -1451,28 +1451,28 @@
         <v>47.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.164031821</v>
       </c>
       <c r="N2">
-        <v>47.3</v>
+        <v>47.135968179</v>
       </c>
       <c r="O2">
-        <v>7.095000000000001</v>
+        <v>7.070395226850001</v>
       </c>
       <c r="P2">
-        <v>40.20500000000001</v>
+        <v>40.06557295215</v>
       </c>
       <c r="Q2">
-        <v>58.30500000000001</v>
+        <v>58.16557295215</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1238685724401964</v>
+        <v>0.1245388581631678</v>
       </c>
       <c r="T2">
-        <v>0.9352413814778209</v>
+        <v>0.9432712317228323</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>288.3586837702668</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1237210195815361</v>
+        <v>0.1235734667228758</v>
       </c>
       <c r="C3">
-        <v>323.1515851773899</v>
+        <v>320.196186922186</v>
       </c>
       <c r="D3">
-        <v>276.8126551773899</v>
+        <v>277.1183269221859</v>
       </c>
       <c r="E3">
-        <v>3.25407</v>
+        <v>6.515140000000001</v>
       </c>
       <c r="F3">
-        <v>3.26107</v>
+        <v>6.52214</v>
       </c>
       <c r="G3">
         <v>49.6</v>
@@ -1533,28 +1533,28 @@
         <v>47.3</v>
       </c>
       <c r="M3">
-        <v>0.164031821</v>
+        <v>0.328063642</v>
       </c>
       <c r="N3">
-        <v>47.135968179</v>
+        <v>46.97193635800001</v>
       </c>
       <c r="O3">
-        <v>7.070395226850001</v>
+        <v>7.045790453700001</v>
       </c>
       <c r="P3">
-        <v>40.06557295215</v>
+        <v>39.92614590430001</v>
       </c>
       <c r="Q3">
-        <v>58.16557295215</v>
+        <v>58.02614590430001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1245388581631678</v>
+        <v>0.125222823186608</v>
       </c>
       <c r="T3">
-        <v>0.9432712317228323</v>
+        <v>0.9514649564626403</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>288.3586837702668</v>
+        <v>144.1793418851334</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1235734667228758</v>
+        <v>0.1234259138642155</v>
       </c>
       <c r="C4">
-        <v>320.196186922186</v>
+        <v>317.2414644923403</v>
       </c>
       <c r="D4">
-        <v>277.1183269221859</v>
+        <v>277.4246744923403</v>
       </c>
       <c r="E4">
-        <v>6.515140000000001</v>
+        <v>9.776210000000001</v>
       </c>
       <c r="F4">
-        <v>6.52214</v>
+        <v>9.78321</v>
       </c>
       <c r="G4">
         <v>49.6</v>
@@ -1615,28 +1615,28 @@
         <v>47.3</v>
       </c>
       <c r="M4">
-        <v>0.328063642</v>
+        <v>0.492095463</v>
       </c>
       <c r="N4">
-        <v>46.97193635800001</v>
+        <v>46.80790453700001</v>
       </c>
       <c r="O4">
-        <v>7.045790453700001</v>
+        <v>7.02118568055</v>
       </c>
       <c r="P4">
-        <v>39.92614590430001</v>
+        <v>39.78671885645001</v>
       </c>
       <c r="Q4">
-        <v>58.02614590430001</v>
+        <v>57.88671885645001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.125222823186608</v>
+        <v>0.1259208905816655</v>
       </c>
       <c r="T4">
-        <v>0.9514649564626403</v>
+        <v>0.9598276239805883</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>144.1793418851334</v>
+        <v>96.11956125675559</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1234259138642155</v>
+        <v>0.1232783610055552</v>
       </c>
       <c r="C5">
-        <v>317.2414644923403</v>
+        <v>314.2874201316587</v>
       </c>
       <c r="D5">
-        <v>277.4246744923403</v>
+        <v>277.7317001316587</v>
       </c>
       <c r="E5">
-        <v>9.776210000000001</v>
+        <v>13.03728</v>
       </c>
       <c r="F5">
-        <v>9.78321</v>
+        <v>13.04428</v>
       </c>
       <c r="G5">
         <v>49.6</v>
@@ -1697,28 +1697,28 @@
         <v>47.3</v>
       </c>
       <c r="M5">
-        <v>0.492095463</v>
+        <v>0.656127284</v>
       </c>
       <c r="N5">
-        <v>46.80790453700001</v>
+        <v>46.643872716</v>
       </c>
       <c r="O5">
-        <v>7.02118568055</v>
+        <v>6.9965809074</v>
       </c>
       <c r="P5">
-        <v>39.78671885645001</v>
+        <v>39.6472918086</v>
       </c>
       <c r="Q5">
-        <v>57.88671885645001</v>
+        <v>57.7472918086</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1259208905816655</v>
+        <v>0.1266335010474534</v>
       </c>
       <c r="T5">
-        <v>0.9598276239805883</v>
+        <v>0.9683645137384936</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>96.11956125675559</v>
+        <v>72.0896709425667</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1232783610055552</v>
+        <v>0.1231308081468949</v>
       </c>
       <c r="C6">
-        <v>314.2874201316587</v>
+        <v>311.3340560938912</v>
       </c>
       <c r="D6">
-        <v>277.7317001316587</v>
+        <v>278.0394060938912</v>
       </c>
       <c r="E6">
-        <v>13.03728</v>
+        <v>16.29835</v>
       </c>
       <c r="F6">
-        <v>13.04428</v>
+        <v>16.30535</v>
       </c>
       <c r="G6">
         <v>49.6</v>
@@ -1779,28 +1779,28 @@
         <v>47.3</v>
       </c>
       <c r="M6">
-        <v>0.656127284</v>
+        <v>0.820159105</v>
       </c>
       <c r="N6">
-        <v>46.643872716</v>
+        <v>46.479840895</v>
       </c>
       <c r="O6">
-        <v>6.9965809074</v>
+        <v>6.97197613425</v>
       </c>
       <c r="P6">
-        <v>39.6472918086</v>
+        <v>39.50786476075</v>
       </c>
       <c r="Q6">
-        <v>57.7472918086</v>
+        <v>57.60786476075</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1266335010474534</v>
+        <v>0.1273611138388368</v>
       </c>
       <c r="T6">
-        <v>0.9683645137384936</v>
+        <v>0.9770811274913024</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>72.0896709425667</v>
+        <v>57.67173675405335</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1231308081468949</v>
+        <v>0.1229832552882346</v>
       </c>
       <c r="C7">
-        <v>311.3340560938912</v>
+        <v>308.3813746427865</v>
       </c>
       <c r="D7">
-        <v>278.0394060938912</v>
+        <v>278.3477946427865</v>
       </c>
       <c r="E7">
-        <v>16.29835</v>
+        <v>19.55942</v>
       </c>
       <c r="F7">
-        <v>16.30535</v>
+        <v>19.56642</v>
       </c>
       <c r="G7">
         <v>49.6</v>
@@ -1861,28 +1861,28 @@
         <v>47.3</v>
       </c>
       <c r="M7">
-        <v>0.820159105</v>
+        <v>0.9841909260000001</v>
       </c>
       <c r="N7">
-        <v>46.479840895</v>
+        <v>46.315809074</v>
       </c>
       <c r="O7">
-        <v>6.97197613425</v>
+        <v>6.9473713611</v>
       </c>
       <c r="P7">
-        <v>39.50786476075</v>
+        <v>39.3684377129</v>
       </c>
       <c r="Q7">
-        <v>57.60786476075</v>
+        <v>57.46843771290001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1273611138388368</v>
+        <v>0.1281042077534411</v>
       </c>
       <c r="T7">
-        <v>0.9770811274913024</v>
+        <v>0.985983201111192</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>57.67173675405335</v>
+        <v>48.05978062837779</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1229832552882346</v>
+        <v>0.1228357024295744</v>
       </c>
       <c r="C8">
-        <v>308.3813746427865</v>
+        <v>305.4293780521482</v>
       </c>
       <c r="D8">
-        <v>278.3477946427865</v>
+        <v>278.6568680521482</v>
       </c>
       <c r="E8">
-        <v>19.55942</v>
+        <v>22.82049</v>
       </c>
       <c r="F8">
-        <v>19.56642</v>
+        <v>22.82749</v>
       </c>
       <c r="G8">
         <v>49.6</v>
@@ -1943,28 +1943,28 @@
         <v>47.3</v>
       </c>
       <c r="M8">
-        <v>0.984190926</v>
+        <v>1.148222747</v>
       </c>
       <c r="N8">
-        <v>46.31580907400001</v>
+        <v>46.15177725300001</v>
       </c>
       <c r="O8">
-        <v>6.947371361100001</v>
+        <v>6.922766587950001</v>
       </c>
       <c r="P8">
-        <v>39.3684377129</v>
+        <v>39.22901066505001</v>
       </c>
       <c r="Q8">
-        <v>57.46843771290001</v>
+        <v>57.32901066505001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1281042077534411</v>
+        <v>0.128863282182338</v>
       </c>
       <c r="T8">
-        <v>0.985983201111192</v>
+        <v>0.9950767171745202</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>48.0597806283778</v>
+        <v>41.19409768146669</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1228357024295743</v>
+        <v>0.1226881495709141</v>
       </c>
       <c r="C9">
-        <v>305.4293780521482</v>
+        <v>302.4780686058899</v>
       </c>
       <c r="D9">
-        <v>278.6568680521482</v>
+        <v>278.9666286058899</v>
       </c>
       <c r="E9">
-        <v>22.82049</v>
+        <v>26.08156</v>
       </c>
       <c r="F9">
-        <v>22.82749</v>
+        <v>26.08856</v>
       </c>
       <c r="G9">
         <v>49.6</v>
@@ -2025,28 +2025,28 @@
         <v>47.3</v>
       </c>
       <c r="M9">
-        <v>1.148222747</v>
+        <v>1.312254568</v>
       </c>
       <c r="N9">
-        <v>46.15177725300001</v>
+        <v>45.987745432</v>
       </c>
       <c r="O9">
-        <v>6.922766587950001</v>
+        <v>6.898161814800001</v>
       </c>
       <c r="P9">
-        <v>39.22901066505001</v>
+        <v>39.08958361720001</v>
       </c>
       <c r="Q9">
-        <v>57.32901066505001</v>
+        <v>57.18958361720001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.128863282182338</v>
+        <v>0.1296388582292544</v>
       </c>
       <c r="T9">
-        <v>0.9950767171745202</v>
+        <v>1.00436791836966</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>41.19409768146668</v>
+        <v>36.04483547128335</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1226881495709141</v>
+        <v>0.1225405967122537</v>
       </c>
       <c r="C10">
-        <v>302.4780686058899</v>
+        <v>299.5274485980924</v>
       </c>
       <c r="D10">
-        <v>278.9666286058899</v>
+        <v>279.2770785980924</v>
       </c>
       <c r="E10">
-        <v>26.08156</v>
+        <v>29.34263</v>
       </c>
       <c r="F10">
-        <v>26.08856</v>
+        <v>29.34963</v>
       </c>
       <c r="G10">
         <v>49.6</v>
@@ -2107,28 +2107,28 @@
         <v>47.3</v>
       </c>
       <c r="M10">
-        <v>1.312254568</v>
+        <v>1.476286389</v>
       </c>
       <c r="N10">
-        <v>45.987745432</v>
+        <v>45.823713611</v>
       </c>
       <c r="O10">
-        <v>6.898161814800001</v>
+        <v>6.87355704165</v>
       </c>
       <c r="P10">
-        <v>39.08958361720001</v>
+        <v>38.95015656935</v>
       </c>
       <c r="Q10">
-        <v>57.18958361720001</v>
+        <v>57.05015656935</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1296388582292544</v>
+        <v>0.1304314799035755</v>
       </c>
       <c r="T10">
-        <v>1.00436791836966</v>
+        <v>1.013863321788868</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>36.04483547128335</v>
+        <v>32.03985375225186</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1225405967122537</v>
+        <v>0.1223930438535935</v>
       </c>
       <c r="C11">
-        <v>299.5274485980924</v>
+        <v>296.5775203330592</v>
       </c>
       <c r="D11">
-        <v>279.2770785980924</v>
+        <v>279.5882203330592</v>
       </c>
       <c r="E11">
-        <v>29.34263</v>
+        <v>32.6037</v>
       </c>
       <c r="F11">
-        <v>29.34963</v>
+        <v>32.6107</v>
       </c>
       <c r="G11">
         <v>49.6</v>
@@ -2189,28 +2189,28 @@
         <v>47.3</v>
       </c>
       <c r="M11">
-        <v>1.476286389</v>
+        <v>1.64031821</v>
       </c>
       <c r="N11">
-        <v>45.823713611</v>
+        <v>45.65968179000001</v>
       </c>
       <c r="O11">
-        <v>6.87355704165</v>
+        <v>6.848952268500001</v>
       </c>
       <c r="P11">
-        <v>38.95015656935</v>
+        <v>38.81072952150001</v>
       </c>
       <c r="Q11">
-        <v>57.05015656935</v>
+        <v>56.91072952150001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1304314799035755</v>
+        <v>0.1312417153928817</v>
       </c>
       <c r="T11">
-        <v>1.013863321788868</v>
+        <v>1.023569734172949</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>32.03985375225186</v>
+        <v>28.83586837702668</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1223930438535935</v>
+        <v>0.1222454909949332</v>
       </c>
       <c r="C12">
-        <v>296.5775203330592</v>
+        <v>293.6282861253745</v>
       </c>
       <c r="D12">
-        <v>279.5882203330592</v>
+        <v>279.9000561253745</v>
       </c>
       <c r="E12">
-        <v>32.6037</v>
+        <v>35.86477000000001</v>
       </c>
       <c r="F12">
-        <v>32.6107</v>
+        <v>35.87177000000001</v>
       </c>
       <c r="G12">
         <v>49.6</v>
@@ -2271,28 +2271,28 @@
         <v>47.3</v>
       </c>
       <c r="M12">
-        <v>1.64031821</v>
+        <v>1.804350031</v>
       </c>
       <c r="N12">
-        <v>45.65968179000001</v>
+        <v>45.49564996900001</v>
       </c>
       <c r="O12">
-        <v>6.848952268500001</v>
+        <v>6.824347495350001</v>
       </c>
       <c r="P12">
-        <v>38.81072952150001</v>
+        <v>38.67130247365</v>
       </c>
       <c r="Q12">
-        <v>56.91072952150001</v>
+        <v>56.77130247365</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1312417153928817</v>
+        <v>0.1320701584212732</v>
       </c>
       <c r="T12">
-        <v>1.023569734172949</v>
+        <v>1.033494268183637</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>28.83586837702668</v>
+        <v>26.21442579729698</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1222454909949332</v>
+        <v>0.1220979381362729</v>
       </c>
       <c r="C13">
-        <v>293.6282861253745</v>
+        <v>290.6797482999603</v>
       </c>
       <c r="D13">
-        <v>279.9000561253745</v>
+        <v>280.2125882999603</v>
       </c>
       <c r="E13">
-        <v>35.86477000000001</v>
+        <v>39.12584</v>
       </c>
       <c r="F13">
-        <v>35.87177000000001</v>
+        <v>39.13284</v>
       </c>
       <c r="G13">
         <v>49.6</v>
@@ -2353,28 +2353,28 @@
         <v>47.3</v>
       </c>
       <c r="M13">
-        <v>1.804350031</v>
+        <v>1.968381852</v>
       </c>
       <c r="N13">
-        <v>45.49564996900001</v>
+        <v>45.331618148</v>
       </c>
       <c r="O13">
-        <v>6.824347495350001</v>
+        <v>6.7997427222</v>
       </c>
       <c r="P13">
-        <v>38.67130247365</v>
+        <v>38.5318754258</v>
       </c>
       <c r="Q13">
-        <v>56.77130247365</v>
+        <v>56.6318754258</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1320701584212732</v>
+        <v>0.1329174297003101</v>
       </c>
       <c r="T13">
-        <v>1.033494268183637</v>
+        <v>1.043644359785477</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.21442579729698</v>
+        <v>24.0298903141889</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1220979381362729</v>
+        <v>0.1219503852776126</v>
       </c>
       <c r="C14">
-        <v>290.6797482999603</v>
+        <v>287.7319091921339</v>
       </c>
       <c r="D14">
-        <v>280.2125882999603</v>
+        <v>280.5258191921339</v>
       </c>
       <c r="E14">
-        <v>39.12584</v>
+        <v>42.38691000000001</v>
       </c>
       <c r="F14">
-        <v>39.13284</v>
+        <v>42.39391000000001</v>
       </c>
       <c r="G14">
         <v>49.6</v>
@@ -2435,28 +2435,28 @@
         <v>47.3</v>
       </c>
       <c r="M14">
-        <v>1.968381852</v>
+        <v>2.132413673</v>
       </c>
       <c r="N14">
-        <v>45.331618148</v>
+        <v>45.167586327</v>
       </c>
       <c r="O14">
-        <v>6.7997427222</v>
+        <v>6.77513794905</v>
       </c>
       <c r="P14">
-        <v>38.5318754258</v>
+        <v>38.39244837795</v>
       </c>
       <c r="Q14">
-        <v>56.6318754258</v>
+        <v>56.49244837795001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1329174297003101</v>
+        <v>0.1337841784800144</v>
       </c>
       <c r="T14">
-        <v>1.043644359785477</v>
+        <v>1.05402778682644</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.0298903141889</v>
+        <v>22.18143721309744</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1219503852776126</v>
+        <v>0.1218028324189522</v>
       </c>
       <c r="C15">
-        <v>287.7319091921339</v>
+        <v>284.7847711476662</v>
       </c>
       <c r="D15">
-        <v>280.5258191921339</v>
+        <v>280.8397511476662</v>
       </c>
       <c r="E15">
-        <v>42.38691000000001</v>
+        <v>45.64798000000001</v>
       </c>
       <c r="F15">
-        <v>42.39391000000001</v>
+        <v>45.65498000000001</v>
       </c>
       <c r="G15">
         <v>49.6</v>
@@ -2517,28 +2517,28 @@
         <v>47.3</v>
       </c>
       <c r="M15">
-        <v>2.132413673</v>
+        <v>2.296445494</v>
       </c>
       <c r="N15">
-        <v>45.167586327</v>
+        <v>45.003554506</v>
       </c>
       <c r="O15">
-        <v>6.77513794905</v>
+        <v>6.7505331759</v>
       </c>
       <c r="P15">
-        <v>38.39244837795</v>
+        <v>38.2530213301</v>
       </c>
       <c r="Q15">
-        <v>56.49244837795001</v>
+        <v>56.3530213301</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1337841784800144</v>
+        <v>0.134671084208084</v>
       </c>
       <c r="T15">
-        <v>1.05402778682644</v>
+        <v>1.064652688914868</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.18143721309744</v>
+        <v>20.59704884073334</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1218028324189522</v>
+        <v>0.121655279560292</v>
       </c>
       <c r="C16">
-        <v>284.7847711476662</v>
+        <v>281.8383365228406</v>
       </c>
       <c r="D16">
-        <v>280.8397511476662</v>
+        <v>281.1543865228405</v>
       </c>
       <c r="E16">
-        <v>45.64798000000001</v>
+        <v>48.90905000000001</v>
       </c>
       <c r="F16">
-        <v>45.65498000000001</v>
+        <v>48.91605000000001</v>
       </c>
       <c r="G16">
         <v>49.6</v>
@@ -2599,28 +2599,28 @@
         <v>47.3</v>
       </c>
       <c r="M16">
-        <v>2.296445494</v>
+        <v>2.460477315</v>
       </c>
       <c r="N16">
-        <v>45.003554506</v>
+        <v>44.83952268500001</v>
       </c>
       <c r="O16">
-        <v>6.7505331759</v>
+        <v>6.725928402750001</v>
       </c>
       <c r="P16">
-        <v>38.2530213301</v>
+        <v>38.11359428225001</v>
       </c>
       <c r="Q16">
-        <v>56.3530213301</v>
+        <v>56.21359428225001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.134671084208084</v>
+        <v>0.1355788583062259</v>
       </c>
       <c r="T16">
-        <v>1.064652688914868</v>
+        <v>1.075527588699494</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.59704884073334</v>
+        <v>19.22391225135112</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.121655279560292</v>
+        <v>0.1215077267016317</v>
       </c>
       <c r="C17">
-        <v>281.8383365228406</v>
+        <v>278.8926076845112</v>
       </c>
       <c r="D17">
-        <v>281.1543865228405</v>
+        <v>281.4697276845112</v>
       </c>
       <c r="E17">
-        <v>48.90905000000001</v>
+        <v>52.17012</v>
       </c>
       <c r="F17">
-        <v>48.91605000000001</v>
+        <v>52.17712</v>
       </c>
       <c r="G17">
         <v>49.6</v>
@@ -2681,28 +2681,28 @@
         <v>47.3</v>
       </c>
       <c r="M17">
-        <v>2.460477315</v>
+        <v>2.624509136</v>
       </c>
       <c r="N17">
-        <v>44.83952268500001</v>
+        <v>44.675490864</v>
       </c>
       <c r="O17">
-        <v>6.725928402750001</v>
+        <v>6.7013236296</v>
       </c>
       <c r="P17">
-        <v>38.11359428225001</v>
+        <v>37.97416723440001</v>
       </c>
       <c r="Q17">
-        <v>56.21359428225001</v>
+        <v>56.07416723440001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1355788583062259</v>
+        <v>0.1365082460733711</v>
       </c>
       <c r="T17">
-        <v>1.075527588699494</v>
+        <v>1.086661414669468</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.22391225135112</v>
+        <v>18.02241773564167</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1215077267016317</v>
+        <v>0.1213601738429714</v>
       </c>
       <c r="C18">
-        <v>278.8926076845112</v>
+        <v>275.9475870101634</v>
       </c>
       <c r="D18">
-        <v>281.4697276845112</v>
+        <v>281.7857770101634</v>
       </c>
       <c r="E18">
-        <v>52.17012</v>
+        <v>55.43119000000001</v>
       </c>
       <c r="F18">
-        <v>52.17712</v>
+        <v>55.43819000000001</v>
       </c>
       <c r="G18">
         <v>49.6</v>
@@ -2763,28 +2763,28 @@
         <v>47.3</v>
       </c>
       <c r="M18">
-        <v>2.624509136</v>
+        <v>2.788540957</v>
       </c>
       <c r="N18">
-        <v>44.675490864</v>
+        <v>44.511459043</v>
       </c>
       <c r="O18">
-        <v>6.7013236296</v>
+        <v>6.67671885645</v>
       </c>
       <c r="P18">
-        <v>37.97416723440001</v>
+        <v>37.83474018655</v>
       </c>
       <c r="Q18">
-        <v>56.07416723440001</v>
+        <v>55.93474018655</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1365082460733711</v>
+        <v>0.1374600287264716</v>
       </c>
       <c r="T18">
-        <v>1.086661414669468</v>
+        <v>1.098063525602574</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.02241773564167</v>
+        <v>16.96227551589804</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1213601738429714</v>
+        <v>0.1212126209843111</v>
       </c>
       <c r="C19">
-        <v>275.9475870101634</v>
+        <v>273.0032768879721</v>
       </c>
       <c r="D19">
-        <v>281.7857770101634</v>
+        <v>282.1025368879721</v>
       </c>
       <c r="E19">
-        <v>55.43119000000001</v>
+        <v>58.69226000000001</v>
       </c>
       <c r="F19">
-        <v>55.43819000000001</v>
+        <v>58.69926000000001</v>
       </c>
       <c r="G19">
         <v>49.6</v>
@@ -2845,28 +2845,28 @@
         <v>47.3</v>
       </c>
       <c r="M19">
-        <v>2.788540957</v>
+        <v>2.952572778</v>
       </c>
       <c r="N19">
-        <v>44.511459043</v>
+        <v>44.34742722200001</v>
       </c>
       <c r="O19">
-        <v>6.67671885645</v>
+        <v>6.652114083300001</v>
       </c>
       <c r="P19">
-        <v>37.83474018655</v>
+        <v>37.69531313870001</v>
       </c>
       <c r="Q19">
-        <v>55.93474018655</v>
+        <v>55.79531313870001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1374600287264716</v>
+        <v>0.1384350255906233</v>
       </c>
       <c r="T19">
-        <v>1.098063525602574</v>
+        <v>1.109743736802341</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.96227551589804</v>
+        <v>16.01992687612593</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1212126209843111</v>
+        <v>0.1210650681256508</v>
       </c>
       <c r="C20">
-        <v>273.0032768879722</v>
+        <v>270.0596797168631</v>
       </c>
       <c r="D20">
-        <v>282.1025368879721</v>
+        <v>282.420009716863</v>
       </c>
       <c r="E20">
-        <v>58.69226</v>
+        <v>61.95333000000001</v>
       </c>
       <c r="F20">
-        <v>58.69926</v>
+        <v>61.96033000000001</v>
       </c>
       <c r="G20">
         <v>49.6</v>
@@ -2927,28 +2927,28 @@
         <v>47.3</v>
       </c>
       <c r="M20">
-        <v>2.952572778</v>
+        <v>3.116604599</v>
       </c>
       <c r="N20">
-        <v>44.34742722200001</v>
+        <v>44.18339540100001</v>
       </c>
       <c r="O20">
-        <v>6.652114083300001</v>
+        <v>6.627509310150001</v>
       </c>
       <c r="P20">
-        <v>37.69531313870001</v>
+        <v>37.55588609085</v>
       </c>
       <c r="Q20">
-        <v>55.79531313870001</v>
+        <v>55.65588609085</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1384350255906233</v>
+        <v>0.1394340964514207</v>
       </c>
       <c r="T20">
-        <v>1.109743736802341</v>
+        <v>1.121712348278646</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.01992687612593</v>
+        <v>15.17677283001404</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1210650681256508</v>
+        <v>0.1209175152669905</v>
       </c>
       <c r="C21">
-        <v>270.0596797168631</v>
+        <v>267.1167979065729</v>
       </c>
       <c r="D21">
-        <v>282.420009716863</v>
+        <v>282.7381979065729</v>
       </c>
       <c r="E21">
-        <v>61.95333000000001</v>
+        <v>65.2144</v>
       </c>
       <c r="F21">
-        <v>61.96033000000001</v>
+        <v>65.2214</v>
       </c>
       <c r="G21">
         <v>49.6</v>
@@ -3009,28 +3009,28 @@
         <v>47.3</v>
       </c>
       <c r="M21">
-        <v>3.116604599</v>
+        <v>3.28063642</v>
       </c>
       <c r="N21">
-        <v>44.18339540100001</v>
+        <v>44.01936358</v>
       </c>
       <c r="O21">
-        <v>6.627509310150001</v>
+        <v>6.602904537000001</v>
       </c>
       <c r="P21">
-        <v>37.55588609085</v>
+        <v>37.416459043</v>
       </c>
       <c r="Q21">
-        <v>55.65588609085</v>
+        <v>55.516459043</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1394340964514207</v>
+        <v>0.1404581440837381</v>
       </c>
       <c r="T21">
-        <v>1.121712348278646</v>
+        <v>1.133980175041858</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.17677283001404</v>
+        <v>14.41793418851334</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1209175152669905</v>
+        <v>0.1207699624083302</v>
       </c>
       <c r="C22">
-        <v>267.1167979065729</v>
+        <v>264.1746338777101</v>
       </c>
       <c r="D22">
-        <v>282.7381979065729</v>
+        <v>283.0571038777101</v>
       </c>
       <c r="E22">
-        <v>65.2144</v>
+        <v>68.47547</v>
       </c>
       <c r="F22">
-        <v>65.2214</v>
+        <v>68.48247000000001</v>
       </c>
       <c r="G22">
         <v>49.6</v>
@@ -3091,28 +3091,28 @@
         <v>47.3</v>
       </c>
       <c r="M22">
-        <v>3.28063642</v>
+        <v>3.444668241</v>
       </c>
       <c r="N22">
-        <v>44.01936358</v>
+        <v>43.855331759</v>
       </c>
       <c r="O22">
-        <v>6.602904537000001</v>
+        <v>6.57829976385</v>
       </c>
       <c r="P22">
-        <v>37.416459043</v>
+        <v>37.27703199515</v>
       </c>
       <c r="Q22">
-        <v>55.516459043</v>
+        <v>55.37703199515001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1404581440837381</v>
+        <v>0.1415081169725699</v>
       </c>
       <c r="T22">
-        <v>1.133980175041858</v>
+        <v>1.146558579697809</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.41793418851334</v>
+        <v>13.73136589382223</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1207699624083302</v>
+        <v>0.1206224095496699</v>
       </c>
       <c r="C23">
-        <v>264.1746338777101</v>
+        <v>261.2331900618167</v>
       </c>
       <c r="D23">
-        <v>283.0571038777101</v>
+        <v>283.3767300618167</v>
       </c>
       <c r="E23">
-        <v>68.47547</v>
+        <v>71.73654000000001</v>
       </c>
       <c r="F23">
-        <v>68.48247000000001</v>
+        <v>71.74354000000001</v>
       </c>
       <c r="G23">
         <v>49.6</v>
@@ -3173,28 +3173,28 @@
         <v>47.3</v>
       </c>
       <c r="M23">
-        <v>3.444668241</v>
+        <v>3.608700062</v>
       </c>
       <c r="N23">
-        <v>43.855331759</v>
+        <v>43.691299938</v>
       </c>
       <c r="O23">
-        <v>6.57829976385</v>
+        <v>6.5536949907</v>
       </c>
       <c r="P23">
-        <v>37.27703199515</v>
+        <v>37.1376049473</v>
       </c>
       <c r="Q23">
-        <v>55.37703199515001</v>
+        <v>55.2376049473</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1415081169725699</v>
+        <v>0.1425850122431666</v>
       </c>
       <c r="T23">
-        <v>1.146558579697809</v>
+        <v>1.159459507550068</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>13.73136589382223</v>
+        <v>13.10721289864849</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1206224095496699</v>
+        <v>0.1207681066910096</v>
       </c>
       <c r="C24">
-        <v>261.2331900618167</v>
+        <v>257.656509220051</v>
       </c>
       <c r="D24">
-        <v>283.3767300618167</v>
+        <v>283.061119220051</v>
       </c>
       <c r="E24">
-        <v>71.73654000000001</v>
+        <v>74.99761000000001</v>
       </c>
       <c r="F24">
-        <v>71.74354000000001</v>
+        <v>75.00461000000001</v>
       </c>
       <c r="G24">
         <v>49.6</v>
@@ -3255,45 +3255,45 @@
         <v>47.3</v>
       </c>
       <c r="M24">
-        <v>3.608700062</v>
+        <v>3.885238798</v>
       </c>
       <c r="N24">
-        <v>43.691299938</v>
+        <v>43.414761202</v>
       </c>
       <c r="O24">
-        <v>6.5536949907</v>
+        <v>6.5122141803</v>
       </c>
       <c r="P24">
-        <v>37.1376049473</v>
+        <v>36.9025470217</v>
       </c>
       <c r="Q24">
-        <v>55.2376049473</v>
+        <v>55.0025470217</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1425850122431666</v>
+        <v>0.143689878819493</v>
       </c>
       <c r="T24">
-        <v>1.159459507550068</v>
+        <v>1.172695524437449</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.15</v>
       </c>
       <c r="W24">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>13.10721289864849</v>
+        <v>12.1742838623841</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1207681066910096</v>
+        <v>0.1206333038323493</v>
       </c>
       <c r="C25">
-        <v>257.656509220051</v>
+        <v>254.6874263964922</v>
       </c>
       <c r="D25">
-        <v>283.061119220051</v>
+        <v>283.3531063964922</v>
       </c>
       <c r="E25">
-        <v>74.99761000000001</v>
+        <v>78.25868000000001</v>
       </c>
       <c r="F25">
-        <v>75.00461000000001</v>
+        <v>78.26568000000002</v>
       </c>
       <c r="G25">
         <v>49.6</v>
@@ -3337,28 +3337,28 @@
         <v>47.3</v>
       </c>
       <c r="M25">
-        <v>3.885238798</v>
+        <v>4.054162224000001</v>
       </c>
       <c r="N25">
-        <v>43.414761202</v>
+        <v>43.245837776</v>
       </c>
       <c r="O25">
-        <v>6.5122141803</v>
+        <v>6.4868756664</v>
       </c>
       <c r="P25">
-        <v>36.9025470217</v>
+        <v>36.7589621096</v>
       </c>
       <c r="Q25">
-        <v>55.0025470217</v>
+        <v>54.8589621096</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.143689878819493</v>
+        <v>0.1448238208320386</v>
       </c>
       <c r="T25">
-        <v>1.172695524437449</v>
+        <v>1.18627985755871</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.1742838623841</v>
+        <v>11.66702203478476</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1206333038323493</v>
+        <v>0.120498500973689</v>
       </c>
       <c r="C26">
-        <v>254.6874263964922</v>
+        <v>251.7189465843767</v>
       </c>
       <c r="D26">
-        <v>283.3531063964922</v>
+        <v>283.6456965843767</v>
       </c>
       <c r="E26">
-        <v>78.25868</v>
+        <v>81.51975</v>
       </c>
       <c r="F26">
-        <v>78.26568</v>
+        <v>81.52675000000001</v>
       </c>
       <c r="G26">
         <v>49.6</v>
@@ -3419,28 +3419,28 @@
         <v>47.3</v>
       </c>
       <c r="M26">
-        <v>4.054162224</v>
+        <v>4.223085650000001</v>
       </c>
       <c r="N26">
-        <v>43.245837776</v>
+        <v>43.07691435</v>
       </c>
       <c r="O26">
-        <v>6.4868756664</v>
+        <v>6.4615371525</v>
       </c>
       <c r="P26">
-        <v>36.7589621096</v>
+        <v>36.6153771975</v>
       </c>
       <c r="Q26">
-        <v>54.8589621096</v>
+        <v>54.7153771975</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1448238208320386</v>
+        <v>0.145988001298252</v>
       </c>
       <c r="T26">
-        <v>1.18627985755871</v>
+        <v>1.200226439563203</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.66702203478476</v>
+        <v>11.20034115339337</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.120498500973689</v>
+        <v>0.1203636981150288</v>
       </c>
       <c r="C27">
-        <v>251.7189465843767</v>
+        <v>248.7510716536426</v>
       </c>
       <c r="D27">
-        <v>283.6456965843767</v>
+        <v>283.9388916536426</v>
       </c>
       <c r="E27">
-        <v>81.51975</v>
+        <v>84.78082000000001</v>
       </c>
       <c r="F27">
-        <v>81.52675000000001</v>
+        <v>84.78782000000001</v>
       </c>
       <c r="G27">
         <v>49.6</v>
@@ -3501,28 +3501,28 @@
         <v>47.3</v>
       </c>
       <c r="M27">
-        <v>4.223085650000001</v>
+        <v>4.392009076000001</v>
       </c>
       <c r="N27">
-        <v>43.07691435</v>
+        <v>42.907990924</v>
       </c>
       <c r="O27">
-        <v>6.4615371525</v>
+        <v>6.436198638600001</v>
       </c>
       <c r="P27">
-        <v>36.6153771975</v>
+        <v>36.4717922854</v>
       </c>
       <c r="Q27">
-        <v>54.7153771975</v>
+        <v>54.5717922854</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.145988001298252</v>
+        <v>0.1471836461013902</v>
       </c>
       <c r="T27">
-        <v>1.200226439563203</v>
+        <v>1.214549956216467</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.20034115339337</v>
+        <v>10.76955880133978</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1203636981150288</v>
+        <v>0.1202288952563685</v>
       </c>
       <c r="C28">
-        <v>248.7510716536426</v>
+        <v>245.7838034819679</v>
       </c>
       <c r="D28">
-        <v>283.9388916536426</v>
+        <v>284.2326934819679</v>
       </c>
       <c r="E28">
-        <v>84.78082000000001</v>
+        <v>88.04189000000001</v>
       </c>
       <c r="F28">
-        <v>84.78782000000001</v>
+        <v>88.04889000000001</v>
       </c>
       <c r="G28">
         <v>49.6</v>
@@ -3583,28 +3583,28 @@
         <v>47.3</v>
       </c>
       <c r="M28">
-        <v>4.392009076000001</v>
+        <v>4.560932502000001</v>
       </c>
       <c r="N28">
-        <v>42.907990924</v>
+        <v>42.739067498</v>
       </c>
       <c r="O28">
-        <v>6.436198638600001</v>
+        <v>6.4108601247</v>
       </c>
       <c r="P28">
-        <v>36.4717922854</v>
+        <v>36.3282073733</v>
       </c>
       <c r="Q28">
-        <v>54.5717922854</v>
+        <v>54.4282073733</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1471836461013902</v>
+        <v>0.1484120482963951</v>
       </c>
       <c r="T28">
-        <v>1.214549956216467</v>
+        <v>1.229265897983519</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.76955880133978</v>
+        <v>10.37068625314201</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1202288952563685</v>
+        <v>0.1200940923977082</v>
       </c>
       <c r="C29">
-        <v>245.7838034819679</v>
+        <v>242.8171439548101</v>
       </c>
       <c r="D29">
-        <v>284.2326934819679</v>
+        <v>284.5271039548101</v>
       </c>
       <c r="E29">
-        <v>88.04189000000001</v>
+        <v>91.30296000000001</v>
       </c>
       <c r="F29">
-        <v>88.04889000000001</v>
+        <v>91.30996000000002</v>
       </c>
       <c r="G29">
         <v>49.6</v>
@@ -3665,28 +3665,28 @@
         <v>47.3</v>
       </c>
       <c r="M29">
-        <v>4.560932502000001</v>
+        <v>4.729855928000001</v>
       </c>
       <c r="N29">
-        <v>42.739067498</v>
+        <v>42.57014407200001</v>
       </c>
       <c r="O29">
-        <v>6.4108601247</v>
+        <v>6.385521610800001</v>
       </c>
       <c r="P29">
-        <v>36.3282073733</v>
+        <v>36.18462246120001</v>
       </c>
       <c r="Q29">
-        <v>54.4282073733</v>
+        <v>54.28462246120001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1484120482963951</v>
+        <v>0.1496745727745947</v>
       </c>
       <c r="T29">
-        <v>1.229265897983519</v>
+        <v>1.244390615910767</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.37068625314201</v>
+        <v>10.00030460124408</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1200940923977082</v>
+        <v>0.1203783395390478</v>
       </c>
       <c r="C30">
-        <v>242.8171439548101</v>
+        <v>238.9359873425781</v>
       </c>
       <c r="D30">
-        <v>284.5271039548101</v>
+        <v>283.9070173425781</v>
       </c>
       <c r="E30">
-        <v>91.30296000000001</v>
+        <v>94.56403000000002</v>
       </c>
       <c r="F30">
-        <v>91.30996000000002</v>
+        <v>94.57103000000002</v>
       </c>
       <c r="G30">
         <v>49.6</v>
@@ -3747,45 +3747,45 @@
         <v>47.3</v>
       </c>
       <c r="M30">
-        <v>4.729855928000001</v>
+        <v>5.059550105000001</v>
       </c>
       <c r="N30">
-        <v>42.57014407200001</v>
+        <v>42.240449895</v>
       </c>
       <c r="O30">
-        <v>6.385521610800001</v>
+        <v>6.336067484250001</v>
       </c>
       <c r="P30">
-        <v>36.18462246120001</v>
+        <v>35.90438241075</v>
       </c>
       <c r="Q30">
-        <v>54.28462246120001</v>
+        <v>54.00438241075</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1496745727745947</v>
+        <v>0.1509726613226026</v>
       </c>
       <c r="T30">
-        <v>1.244390615910767</v>
+        <v>1.259941382230332</v>
       </c>
       <c r="U30">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V30">
         <v>0.15</v>
       </c>
       <c r="W30">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>10.00030460124408</v>
+        <v>9.348657295291277</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1203783395390478</v>
+        <v>0.1202579866803876</v>
       </c>
       <c r="C31">
-        <v>238.9359873425781</v>
+        <v>235.9371375025545</v>
       </c>
       <c r="D31">
-        <v>283.9070173425781</v>
+        <v>284.1692375025545</v>
       </c>
       <c r="E31">
-        <v>94.56403</v>
+        <v>97.82510000000001</v>
       </c>
       <c r="F31">
-        <v>94.57103000000001</v>
+        <v>97.83210000000001</v>
       </c>
       <c r="G31">
         <v>49.6</v>
@@ -3829,28 +3829,28 @@
         <v>47.3</v>
       </c>
       <c r="M31">
-        <v>5.059550105</v>
+        <v>5.23401735</v>
       </c>
       <c r="N31">
-        <v>42.240449895</v>
+        <v>42.06598265</v>
       </c>
       <c r="O31">
-        <v>6.336067484250001</v>
+        <v>6.3098973975</v>
       </c>
       <c r="P31">
-        <v>35.90438241075</v>
+        <v>35.7560852525</v>
       </c>
       <c r="Q31">
-        <v>54.00438241075</v>
+        <v>53.8560852525</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1509726613226026</v>
+        <v>0.1523078381148394</v>
       </c>
       <c r="T31">
-        <v>1.259941382230332</v>
+        <v>1.275936456159027</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.348657295291277</v>
+        <v>9.037035385448235</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1202579866803876</v>
+        <v>0.1201376338217273</v>
       </c>
       <c r="C32">
-        <v>235.9371375025545</v>
+        <v>232.938772490125</v>
       </c>
       <c r="D32">
-        <v>284.1692375025545</v>
+        <v>284.431942490125</v>
       </c>
       <c r="E32">
-        <v>97.82510000000001</v>
+        <v>101.08617</v>
       </c>
       <c r="F32">
-        <v>97.83210000000001</v>
+        <v>101.09317</v>
       </c>
       <c r="G32">
         <v>49.6</v>
@@ -3911,28 +3911,28 @@
         <v>47.3</v>
       </c>
       <c r="M32">
-        <v>5.23401735</v>
+        <v>5.408484595000001</v>
       </c>
       <c r="N32">
-        <v>42.06598265</v>
+        <v>41.89151540500001</v>
       </c>
       <c r="O32">
-        <v>6.3098973975</v>
+        <v>6.283727310750001</v>
       </c>
       <c r="P32">
-        <v>35.7560852525</v>
+        <v>35.60778809425</v>
       </c>
       <c r="Q32">
-        <v>53.8560852525</v>
+        <v>53.70778809425001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1523078381148394</v>
+        <v>0.1536817156836627</v>
       </c>
       <c r="T32">
-        <v>1.275936456159027</v>
+        <v>1.292395155418989</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.037035385448235</v>
+        <v>8.745518114949906</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1201376338217273</v>
+        <v>0.1200172809630669</v>
       </c>
       <c r="C33">
-        <v>232.938772490125</v>
+        <v>229.9408936511548</v>
       </c>
       <c r="D33">
-        <v>284.431942490125</v>
+        <v>284.6951336511548</v>
       </c>
       <c r="E33">
-        <v>101.08617</v>
+        <v>104.34724</v>
       </c>
       <c r="F33">
-        <v>101.09317</v>
+        <v>104.35424</v>
       </c>
       <c r="G33">
         <v>49.6</v>
@@ -3993,28 +3993,28 @@
         <v>47.3</v>
       </c>
       <c r="M33">
-        <v>5.408484595000001</v>
+        <v>5.58295184</v>
       </c>
       <c r="N33">
-        <v>41.89151540500001</v>
+        <v>41.71704816</v>
       </c>
       <c r="O33">
-        <v>6.283727310750001</v>
+        <v>6.257557224</v>
       </c>
       <c r="P33">
-        <v>35.60778809425</v>
+        <v>35.459490936</v>
       </c>
       <c r="Q33">
-        <v>53.70778809425001</v>
+        <v>53.559490936</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1536817156836627</v>
+        <v>0.1550960014162749</v>
       </c>
       <c r="T33">
-        <v>1.292395155418989</v>
+        <v>1.309337934068949</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.745518114949906</v>
+        <v>8.472220673857722</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1200172809630669</v>
+        <v>0.1198969281044067</v>
       </c>
       <c r="C34">
-        <v>229.9408936511548</v>
+        <v>226.9435023364947</v>
       </c>
       <c r="D34">
-        <v>284.6951336511548</v>
+        <v>284.9588123364947</v>
       </c>
       <c r="E34">
-        <v>104.34724</v>
+        <v>107.60831</v>
       </c>
       <c r="F34">
-        <v>104.35424</v>
+        <v>107.61531</v>
       </c>
       <c r="G34">
         <v>49.6</v>
@@ -4075,28 +4075,28 @@
         <v>47.3</v>
       </c>
       <c r="M34">
-        <v>5.58295184</v>
+        <v>5.757419085</v>
       </c>
       <c r="N34">
-        <v>41.71704816</v>
+        <v>41.542580915</v>
       </c>
       <c r="O34">
-        <v>6.257557224</v>
+        <v>6.23138713725</v>
       </c>
       <c r="P34">
-        <v>35.459490936</v>
+        <v>35.31119377775</v>
       </c>
       <c r="Q34">
-        <v>53.559490936</v>
+        <v>53.41119377775</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1550960014162749</v>
+        <v>0.1565525046334428</v>
       </c>
       <c r="T34">
-        <v>1.309337934068949</v>
+        <v>1.326786467305476</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.472220673857722</v>
+        <v>8.21548671404385</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1198969281044067</v>
+        <v>0.1197765752457464</v>
       </c>
       <c r="C35">
-        <v>226.9435023364947</v>
+        <v>223.9465999020051</v>
       </c>
       <c r="D35">
-        <v>284.9588123364947</v>
+        <v>285.2229799020051</v>
       </c>
       <c r="E35">
-        <v>107.60831</v>
+        <v>110.86938</v>
       </c>
       <c r="F35">
-        <v>107.61531</v>
+        <v>110.87638</v>
       </c>
       <c r="G35">
         <v>49.6</v>
@@ -4157,28 +4157,28 @@
         <v>47.3</v>
       </c>
       <c r="M35">
-        <v>5.757419085</v>
+        <v>5.93188633</v>
       </c>
       <c r="N35">
-        <v>41.542580915</v>
+        <v>41.36811367000001</v>
       </c>
       <c r="O35">
-        <v>6.23138713725</v>
+        <v>6.205217050500001</v>
       </c>
       <c r="P35">
-        <v>35.31119377775</v>
+        <v>35.1628966195</v>
       </c>
       <c r="Q35">
-        <v>53.41119377775</v>
+        <v>53.2628966195</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1565525046334428</v>
+        <v>0.1580531443117369</v>
       </c>
       <c r="T35">
-        <v>1.326786467305476</v>
+        <v>1.344763743973412</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.21548671404385</v>
+        <v>7.97385475186609</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1197765752457464</v>
+        <v>0.1196562223870861</v>
       </c>
       <c r="C36">
-        <v>223.9465999020051</v>
+        <v>220.9501877085788</v>
       </c>
       <c r="D36">
-        <v>285.2229799020051</v>
+        <v>285.4876377085788</v>
       </c>
       <c r="E36">
-        <v>110.86938</v>
+        <v>114.13045</v>
       </c>
       <c r="F36">
-        <v>110.87638</v>
+        <v>114.13745</v>
       </c>
       <c r="G36">
         <v>49.6</v>
@@ -4239,28 +4239,28 @@
         <v>47.3</v>
       </c>
       <c r="M36">
-        <v>5.93188633</v>
+        <v>6.106353575000001</v>
       </c>
       <c r="N36">
-        <v>41.36811367000001</v>
+        <v>41.193646425</v>
       </c>
       <c r="O36">
-        <v>6.205217050500001</v>
+        <v>6.17904696375</v>
       </c>
       <c r="P36">
-        <v>35.1628966195</v>
+        <v>35.01459946125</v>
       </c>
       <c r="Q36">
-        <v>53.2628966195</v>
+        <v>53.11459946125</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1580531443117369</v>
+        <v>0.159599957518594</v>
       </c>
       <c r="T36">
-        <v>1.344763743973412</v>
+        <v>1.363294167615747</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.97385475186609</v>
+        <v>7.746030330384201</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1196562223870861</v>
+        <v>0.1197806695284258</v>
       </c>
       <c r="C37">
-        <v>220.9501877085788</v>
+        <v>217.4154651409146</v>
       </c>
       <c r="D37">
-        <v>285.4876377085788</v>
+        <v>285.2139851409146</v>
       </c>
       <c r="E37">
-        <v>114.13045</v>
+        <v>117.39152</v>
       </c>
       <c r="F37">
-        <v>114.13745</v>
+        <v>117.39852</v>
       </c>
       <c r="G37">
         <v>49.6</v>
@@ -4321,45 +4321,45 @@
         <v>47.3</v>
       </c>
       <c r="M37">
-        <v>6.106353575000001</v>
+        <v>6.374739636000001</v>
       </c>
       <c r="N37">
-        <v>41.193646425</v>
+        <v>40.925260364</v>
       </c>
       <c r="O37">
-        <v>6.17904696375</v>
+        <v>6.1387890546</v>
       </c>
       <c r="P37">
-        <v>35.01459946125</v>
+        <v>34.7864713094</v>
       </c>
       <c r="Q37">
-        <v>53.11459946125</v>
+        <v>52.8864713094</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.159599957518594</v>
+        <v>0.1611951086381653</v>
       </c>
       <c r="T37">
-        <v>1.363294167615747</v>
+        <v>1.382403666996904</v>
       </c>
       <c r="U37">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V37">
         <v>0.15</v>
       </c>
       <c r="W37">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y37">
-        <v>7.746030330384201</v>
+        <v>7.419910882772875</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1197806695284258</v>
+        <v>0.1196671166697655</v>
       </c>
       <c r="C38">
-        <v>217.4154651409146</v>
+        <v>214.4040707961816</v>
       </c>
       <c r="D38">
-        <v>285.2139851409146</v>
+        <v>285.4636607961816</v>
       </c>
       <c r="E38">
-        <v>117.39152</v>
+        <v>120.65259</v>
       </c>
       <c r="F38">
-        <v>117.39852</v>
+        <v>120.65959</v>
       </c>
       <c r="G38">
         <v>49.6</v>
@@ -4403,28 +4403,28 @@
         <v>47.3</v>
       </c>
       <c r="M38">
-        <v>6.374739636</v>
+        <v>6.551815737000001</v>
       </c>
       <c r="N38">
-        <v>40.925260364</v>
+        <v>40.74818426300001</v>
       </c>
       <c r="O38">
-        <v>6.1387890546</v>
+        <v>6.11222763945</v>
       </c>
       <c r="P38">
-        <v>34.7864713094</v>
+        <v>34.63595662355001</v>
       </c>
       <c r="Q38">
-        <v>52.8864713094</v>
+        <v>52.73595662355001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1611951086381653</v>
+        <v>0.1628408994758183</v>
       </c>
       <c r="T38">
-        <v>1.382403666996904</v>
+        <v>1.402119817152066</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.419910882772876</v>
+        <v>7.219372750806041</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1196671166697655</v>
+        <v>0.1195535638111052</v>
       </c>
       <c r="C39">
-        <v>214.4040707961816</v>
+        <v>211.3931139654161</v>
       </c>
       <c r="D39">
-        <v>285.4636607961816</v>
+        <v>285.7137739654161</v>
       </c>
       <c r="E39">
-        <v>120.65259</v>
+        <v>123.91366</v>
       </c>
       <c r="F39">
-        <v>120.65959</v>
+        <v>123.92066</v>
       </c>
       <c r="G39">
         <v>49.6</v>
@@ -4485,28 +4485,28 @@
         <v>47.3</v>
       </c>
       <c r="M39">
-        <v>6.551815737000001</v>
+        <v>6.728891838000001</v>
       </c>
       <c r="N39">
-        <v>40.74818426300001</v>
+        <v>40.571108162</v>
       </c>
       <c r="O39">
-        <v>6.11222763945</v>
+        <v>6.0856662243</v>
       </c>
       <c r="P39">
-        <v>34.63595662355001</v>
+        <v>34.4854419377</v>
       </c>
       <c r="Q39">
-        <v>52.73595662355001</v>
+        <v>52.5854419377</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1628408994758183</v>
+        <v>0.1645397803404923</v>
       </c>
       <c r="T39">
-        <v>1.402119817152066</v>
+        <v>1.422471972150944</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.219372750806041</v>
+        <v>7.029389257363777</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1195535638111052</v>
+        <v>0.1194400109524449</v>
       </c>
       <c r="C40">
-        <v>211.3931139654161</v>
+        <v>208.3825957996297</v>
       </c>
       <c r="D40">
-        <v>285.7137739654161</v>
+        <v>285.9643257996296</v>
       </c>
       <c r="E40">
-        <v>123.91366</v>
+        <v>127.17473</v>
       </c>
       <c r="F40">
-        <v>123.92066</v>
+        <v>127.18173</v>
       </c>
       <c r="G40">
         <v>49.6</v>
@@ -4567,28 +4567,28 @@
         <v>47.3</v>
       </c>
       <c r="M40">
-        <v>6.728891838000001</v>
+        <v>6.905967939000001</v>
       </c>
       <c r="N40">
-        <v>40.571108162</v>
+        <v>40.394032061</v>
       </c>
       <c r="O40">
-        <v>6.0856662243</v>
+        <v>6.059104809150001</v>
       </c>
       <c r="P40">
-        <v>34.4854419377</v>
+        <v>34.33492725185</v>
       </c>
       <c r="Q40">
-        <v>52.5854419377</v>
+        <v>52.43492725185001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1645397803404923</v>
+        <v>0.1662943622171228</v>
       </c>
       <c r="T40">
-        <v>1.422471972150944</v>
+        <v>1.443491410920276</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.029389257363777</v>
+        <v>6.849148507174962</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1194400109524449</v>
+        <v>0.1193264580937846</v>
       </c>
       <c r="C41">
-        <v>208.3825957996297</v>
+        <v>205.3725174538742</v>
       </c>
       <c r="D41">
-        <v>285.9643257996296</v>
+        <v>286.2153174538742</v>
       </c>
       <c r="E41">
-        <v>127.17473</v>
+        <v>130.4358</v>
       </c>
       <c r="F41">
-        <v>127.18173</v>
+        <v>130.4428</v>
       </c>
       <c r="G41">
         <v>49.6</v>
@@ -4649,28 +4649,28 @@
         <v>47.3</v>
       </c>
       <c r="M41">
-        <v>6.905967939000001</v>
+        <v>7.083044040000001</v>
       </c>
       <c r="N41">
-        <v>40.394032061</v>
+        <v>40.21695596000001</v>
       </c>
       <c r="O41">
-        <v>6.059104809150001</v>
+        <v>6.032543394000001</v>
       </c>
       <c r="P41">
-        <v>34.33492725185</v>
+        <v>34.18441256600001</v>
       </c>
       <c r="Q41">
-        <v>52.43492725185001</v>
+        <v>52.28441256600001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1662943622171228</v>
+        <v>0.1681074301563077</v>
       </c>
       <c r="T41">
-        <v>1.443491410920276</v>
+        <v>1.465211497648586</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.849148507174962</v>
+        <v>6.677919794495589</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1193264580937846</v>
+        <v>0.1192129052351243</v>
       </c>
       <c r="C42">
-        <v>205.3725174538742</v>
+        <v>202.362880087261</v>
       </c>
       <c r="D42">
-        <v>286.2153174538742</v>
+        <v>286.466750087261</v>
       </c>
       <c r="E42">
-        <v>130.4358</v>
+        <v>133.69687</v>
       </c>
       <c r="F42">
-        <v>130.4428</v>
+        <v>133.70387</v>
       </c>
       <c r="G42">
         <v>49.6</v>
@@ -4731,28 +4731,28 @@
         <v>47.3</v>
       </c>
       <c r="M42">
-        <v>7.083044040000001</v>
+        <v>7.260120141000002</v>
       </c>
       <c r="N42">
-        <v>40.21695596000001</v>
+        <v>40.039879859</v>
       </c>
       <c r="O42">
-        <v>6.032543394000001</v>
+        <v>6.00598197885</v>
       </c>
       <c r="P42">
-        <v>34.18441256600001</v>
+        <v>34.03389788015</v>
       </c>
       <c r="Q42">
-        <v>52.28441256600001</v>
+        <v>52.13389788015</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1681074301563077</v>
+        <v>0.1699819580256345</v>
       </c>
       <c r="T42">
-        <v>1.465211497648586</v>
+        <v>1.48766785850328</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.677919794495589</v>
+        <v>6.515043701946914</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1192129052351243</v>
+        <v>0.119099352376464</v>
       </c>
       <c r="C43">
-        <v>202.362880087261</v>
+        <v>199.3536848629776</v>
       </c>
       <c r="D43">
-        <v>286.466750087261</v>
+        <v>286.7186248629775</v>
       </c>
       <c r="E43">
-        <v>133.69687</v>
+        <v>136.95794</v>
       </c>
       <c r="F43">
-        <v>133.70387</v>
+        <v>136.96494</v>
       </c>
       <c r="G43">
         <v>49.6</v>
@@ -4813,28 +4813,28 @@
         <v>47.3</v>
       </c>
       <c r="M43">
-        <v>7.260120141000002</v>
+        <v>7.437196242000001</v>
       </c>
       <c r="N43">
-        <v>40.039879859</v>
+        <v>39.86280375800001</v>
       </c>
       <c r="O43">
-        <v>6.00598197885</v>
+        <v>5.979420563700001</v>
       </c>
       <c r="P43">
-        <v>34.03389788015</v>
+        <v>33.8833831943</v>
       </c>
       <c r="Q43">
-        <v>52.13389788015</v>
+        <v>51.9833831943</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1699819580256345</v>
+        <v>0.171921124787007</v>
       </c>
       <c r="T43">
-        <v>1.48766785850328</v>
+        <v>1.510898576628825</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.515043701946914</v>
+        <v>6.359923613805322</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.119099352376464</v>
+        <v>0.1189857995178037</v>
       </c>
       <c r="C44">
-        <v>199.3536848629776</v>
+        <v>196.344932948306</v>
       </c>
       <c r="D44">
-        <v>286.7186248629775</v>
+        <v>286.970942948306</v>
       </c>
       <c r="E44">
-        <v>136.95794</v>
+        <v>140.21901</v>
       </c>
       <c r="F44">
-        <v>136.96494</v>
+        <v>140.22601</v>
       </c>
       <c r="G44">
         <v>49.6</v>
@@ -4895,28 +4895,28 @@
         <v>47.3</v>
       </c>
       <c r="M44">
-        <v>7.437196242000001</v>
+        <v>7.614272343000001</v>
       </c>
       <c r="N44">
-        <v>39.86280375800001</v>
+        <v>39.685727657</v>
       </c>
       <c r="O44">
-        <v>5.979420563700001</v>
+        <v>5.95285914855</v>
       </c>
       <c r="P44">
-        <v>33.8833831943</v>
+        <v>33.73286850845</v>
       </c>
       <c r="Q44">
-        <v>51.9833831943</v>
+        <v>51.83286850845001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1719211247870069</v>
+        <v>0.173928332487375</v>
       </c>
       <c r="T44">
-        <v>1.510898576628824</v>
+        <v>1.534944407671055</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.359923613805322</v>
+        <v>6.212018413484268</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1189857995178037</v>
+        <v>0.1192462466591434</v>
       </c>
       <c r="C45">
-        <v>196.344932948306</v>
+        <v>192.5057985632101</v>
       </c>
       <c r="D45">
-        <v>286.970942948306</v>
+        <v>286.3928785632101</v>
       </c>
       <c r="E45">
-        <v>140.21901</v>
+        <v>143.48008</v>
       </c>
       <c r="F45">
-        <v>140.22601</v>
+        <v>143.48708</v>
       </c>
       <c r="G45">
         <v>49.6</v>
@@ -4977,45 +4977,45 @@
         <v>47.3</v>
       </c>
       <c r="M45">
-        <v>7.614272343000001</v>
+        <v>7.934835524000001</v>
       </c>
       <c r="N45">
-        <v>39.685727657</v>
+        <v>39.365164476</v>
       </c>
       <c r="O45">
-        <v>5.95285914855</v>
+        <v>5.9047746714</v>
       </c>
       <c r="P45">
-        <v>33.73286850845</v>
+        <v>33.46038980460001</v>
       </c>
       <c r="Q45">
-        <v>51.83286850845001</v>
+        <v>51.56038980460001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.173928332487375</v>
+        <v>0.1760072261770418</v>
       </c>
       <c r="T45">
-        <v>1.534944407671055</v>
+        <v>1.559849018393365</v>
       </c>
       <c r="U45">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.15</v>
       </c>
       <c r="W45">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>6.212018413484268</v>
+        <v>5.961056137450442</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1192462466591434</v>
+        <v>0.1191411938004831</v>
       </c>
       <c r="C46">
-        <v>192.5057985632101</v>
+        <v>189.4776137113282</v>
       </c>
       <c r="D46">
-        <v>286.3928785632101</v>
+        <v>286.6257637113282</v>
       </c>
       <c r="E46">
-        <v>143.48008</v>
+        <v>146.74115</v>
       </c>
       <c r="F46">
-        <v>143.48708</v>
+        <v>146.74815</v>
       </c>
       <c r="G46">
         <v>49.6</v>
@@ -5059,28 +5059,28 @@
         <v>47.3</v>
       </c>
       <c r="M46">
-        <v>7.934835524000001</v>
+        <v>8.115172695</v>
       </c>
       <c r="N46">
-        <v>39.365164476</v>
+        <v>39.18482730500001</v>
       </c>
       <c r="O46">
-        <v>5.9047746714</v>
+        <v>5.877724095750001</v>
       </c>
       <c r="P46">
-        <v>33.46038980460001</v>
+        <v>33.30710320925</v>
       </c>
       <c r="Q46">
-        <v>51.56038980460001</v>
+        <v>51.40710320925</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1760072261770418</v>
+        <v>0.1781617160008784</v>
       </c>
       <c r="T46">
-        <v>1.559849018393365</v>
+        <v>1.58565925132376</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.961056137450442</v>
+        <v>5.828588223284878</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1191411938004831</v>
+        <v>0.1190361409418229</v>
       </c>
       <c r="C47">
-        <v>189.4776137113282</v>
+        <v>186.4498079165715</v>
       </c>
       <c r="D47">
-        <v>286.6257637113282</v>
+        <v>286.8590279165715</v>
       </c>
       <c r="E47">
-        <v>146.74115</v>
+        <v>150.00222</v>
       </c>
       <c r="F47">
-        <v>146.74815</v>
+        <v>150.00922</v>
       </c>
       <c r="G47">
         <v>49.6</v>
@@ -5141,28 +5141,28 @@
         <v>47.3</v>
       </c>
       <c r="M47">
-        <v>8.115172695</v>
+        <v>8.295509866000002</v>
       </c>
       <c r="N47">
-        <v>39.18482730500001</v>
+        <v>39.004490134</v>
       </c>
       <c r="O47">
-        <v>5.877724095750001</v>
+        <v>5.8506735201</v>
       </c>
       <c r="P47">
-        <v>33.30710320925</v>
+        <v>33.1538166139</v>
       </c>
       <c r="Q47">
-        <v>51.40710320925</v>
+        <v>51.2538166139</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1781617160008784</v>
+        <v>0.1803960017441164</v>
       </c>
       <c r="T47">
-        <v>1.58565925132376</v>
+        <v>1.612425418807132</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.828588223284878</v>
+        <v>5.701879783648248</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1190361409418229</v>
+        <v>0.1189310880831626</v>
       </c>
       <c r="C48">
-        <v>186.4498079165715</v>
+        <v>183.4223821051562</v>
       </c>
       <c r="D48">
-        <v>286.8590279165715</v>
+        <v>287.0926721051562</v>
       </c>
       <c r="E48">
-        <v>150.00222</v>
+        <v>153.26329</v>
       </c>
       <c r="F48">
-        <v>150.00922</v>
+        <v>153.27029</v>
       </c>
       <c r="G48">
         <v>49.6</v>
@@ -5223,28 +5223,28 @@
         <v>47.3</v>
       </c>
       <c r="M48">
-        <v>8.295509866000002</v>
+        <v>8.475847037000001</v>
       </c>
       <c r="N48">
-        <v>39.004490134</v>
+        <v>38.824152963</v>
       </c>
       <c r="O48">
-        <v>5.8506735201</v>
+        <v>5.82362294445</v>
       </c>
       <c r="P48">
-        <v>33.1538166139</v>
+        <v>33.00053001855</v>
       </c>
       <c r="Q48">
-        <v>51.2538166139</v>
+        <v>51.10053001855</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1803960017441164</v>
+        <v>0.1827146001569105</v>
       </c>
       <c r="T48">
-        <v>1.612425418807132</v>
+        <v>1.64020163034648</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.701879783648248</v>
+        <v>5.580563192506797</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1189310880831626</v>
+        <v>0.1188260352245023</v>
       </c>
       <c r="C49">
-        <v>183.4223821051562</v>
+        <v>180.3953372063184</v>
       </c>
       <c r="D49">
-        <v>287.0926721051562</v>
+        <v>287.3266972063184</v>
       </c>
       <c r="E49">
-        <v>153.26329</v>
+        <v>156.52436</v>
       </c>
       <c r="F49">
-        <v>153.27029</v>
+        <v>156.53136</v>
       </c>
       <c r="G49">
         <v>49.6</v>
@@ -5305,28 +5305,28 @@
         <v>47.3</v>
       </c>
       <c r="M49">
-        <v>8.475847037000001</v>
+        <v>8.656184208000003</v>
       </c>
       <c r="N49">
-        <v>38.824152963</v>
+        <v>38.643815792</v>
       </c>
       <c r="O49">
-        <v>5.82362294445</v>
+        <v>5.7965723688</v>
       </c>
       <c r="P49">
-        <v>33.00053001855</v>
+        <v>32.8472434232</v>
       </c>
       <c r="Q49">
-        <v>51.10053001855</v>
+        <v>50.9472434232</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1827146001569105</v>
+        <v>0.1851223754317351</v>
       </c>
       <c r="T49">
-        <v>1.64020163034648</v>
+        <v>1.669046157714265</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.580563192506797</v>
+        <v>5.464301459329571</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1188260352245023</v>
+        <v>0.118720982365842</v>
       </c>
       <c r="C50">
-        <v>180.3953372063184</v>
+        <v>177.3686741523269</v>
       </c>
       <c r="D50">
-        <v>287.3266972063184</v>
+        <v>287.5611041523269</v>
       </c>
       <c r="E50">
-        <v>156.52436</v>
+        <v>159.78543</v>
       </c>
       <c r="F50">
-        <v>156.53136</v>
+        <v>159.79243</v>
       </c>
       <c r="G50">
         <v>49.6</v>
@@ -5387,28 +5387,28 @@
         <v>47.3</v>
       </c>
       <c r="M50">
-        <v>8.656184208000001</v>
+        <v>8.836521379000002</v>
       </c>
       <c r="N50">
-        <v>38.64381579200001</v>
+        <v>38.463478621</v>
       </c>
       <c r="O50">
-        <v>5.796572368800001</v>
+        <v>5.76952179315</v>
       </c>
       <c r="P50">
-        <v>32.84724342320001</v>
+        <v>32.69395682785</v>
       </c>
       <c r="Q50">
-        <v>50.94724342320001</v>
+        <v>50.79395682785</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1851223754317351</v>
+        <v>0.1876245732663568</v>
       </c>
       <c r="T50">
-        <v>1.669046157714265</v>
+        <v>1.699021843018041</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.464301459329572</v>
+        <v>5.352785103016723</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.118720982365842</v>
+        <v>0.1186159295071817</v>
       </c>
       <c r="C51">
-        <v>177.3686741523269</v>
+        <v>174.3423938784948</v>
       </c>
       <c r="D51">
-        <v>287.5611041523269</v>
+        <v>287.7958938784948</v>
       </c>
       <c r="E51">
-        <v>159.78543</v>
+        <v>163.0465</v>
       </c>
       <c r="F51">
-        <v>159.79243</v>
+        <v>163.0535</v>
       </c>
       <c r="G51">
         <v>49.6</v>
@@ -5469,28 +5469,28 @@
         <v>47.3</v>
       </c>
       <c r="M51">
-        <v>8.836521379000002</v>
+        <v>9.01685855</v>
       </c>
       <c r="N51">
-        <v>38.463478621</v>
+        <v>38.28314145</v>
       </c>
       <c r="O51">
-        <v>5.76952179315</v>
+        <v>5.7424712175</v>
       </c>
       <c r="P51">
-        <v>32.69395682785</v>
+        <v>32.54067023250001</v>
       </c>
       <c r="Q51">
-        <v>50.79395682785</v>
+        <v>50.64067023250001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1876245732663568</v>
+        <v>0.1902268590143634</v>
       </c>
       <c r="T51">
-        <v>1.699021843018041</v>
+        <v>1.730196555733969</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.352785103016723</v>
+        <v>5.24572940095639</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1186159295071817</v>
+        <v>0.1185108766485214</v>
       </c>
       <c r="C52">
-        <v>174.3423938784948</v>
+        <v>171.3164973231929</v>
       </c>
       <c r="D52">
-        <v>287.7958938784948</v>
+        <v>288.0310673231929</v>
       </c>
       <c r="E52">
-        <v>163.0465</v>
+        <v>166.30757</v>
       </c>
       <c r="F52">
-        <v>163.0535</v>
+        <v>166.31457</v>
       </c>
       <c r="G52">
         <v>49.6</v>
@@ -5551,28 +5551,28 @@
         <v>47.3</v>
       </c>
       <c r="M52">
-        <v>9.01685855</v>
+        <v>9.197195721</v>
       </c>
       <c r="N52">
-        <v>38.28314145</v>
+        <v>38.102804279</v>
       </c>
       <c r="O52">
-        <v>5.7424712175</v>
+        <v>5.715420641850001</v>
       </c>
       <c r="P52">
-        <v>32.54067023250001</v>
+        <v>32.38738363715</v>
       </c>
       <c r="Q52">
-        <v>50.64067023250001</v>
+        <v>50.48738363715</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1902268590143634</v>
+        <v>0.1929353605071865</v>
       </c>
       <c r="T52">
-        <v>1.730196555733969</v>
+        <v>1.762643705703607</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.24572940095639</v>
+        <v>5.142871961721951</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1185108766485214</v>
+        <v>0.1184058237898611</v>
       </c>
       <c r="C53">
-        <v>171.3164973231929</v>
+        <v>168.2909854278613</v>
       </c>
       <c r="D53">
-        <v>288.0310673231929</v>
+        <v>288.2666254278613</v>
       </c>
       <c r="E53">
-        <v>166.30757</v>
+        <v>169.56864</v>
       </c>
       <c r="F53">
-        <v>166.31457</v>
+        <v>169.57564</v>
       </c>
       <c r="G53">
         <v>49.6</v>
@@ -5633,28 +5633,28 @@
         <v>47.3</v>
       </c>
       <c r="M53">
-        <v>9.197195721</v>
+        <v>9.377532892000001</v>
       </c>
       <c r="N53">
-        <v>38.102804279</v>
+        <v>37.92246710800001</v>
       </c>
       <c r="O53">
-        <v>5.715420641850001</v>
+        <v>5.688370066200001</v>
       </c>
       <c r="P53">
-        <v>32.38738363715</v>
+        <v>32.23409704180001</v>
       </c>
       <c r="Q53">
-        <v>50.48738363715</v>
+        <v>50.33409704180001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1929353605071865</v>
+        <v>0.1957567162288773</v>
       </c>
       <c r="T53">
-        <v>1.762643705703607</v>
+        <v>1.796442820255314</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.142871961721951</v>
+        <v>5.043970577842682</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1184058237898611</v>
+        <v>0.1183007709312008</v>
       </c>
       <c r="C54">
-        <v>168.2909854278613</v>
+        <v>165.2658591370225</v>
       </c>
       <c r="D54">
-        <v>288.2666254278613</v>
+        <v>288.5025691370225</v>
       </c>
       <c r="E54">
-        <v>169.56864</v>
+        <v>172.82971</v>
       </c>
       <c r="F54">
-        <v>169.57564</v>
+        <v>172.83671</v>
       </c>
       <c r="G54">
         <v>49.6</v>
@@ -5715,28 +5715,28 @@
         <v>47.3</v>
       </c>
       <c r="M54">
-        <v>9.377532892000001</v>
+        <v>9.557870063000001</v>
       </c>
       <c r="N54">
-        <v>37.92246710800001</v>
+        <v>37.742129937</v>
       </c>
       <c r="O54">
-        <v>5.688370066200001</v>
+        <v>5.66131949055</v>
       </c>
       <c r="P54">
-        <v>32.23409704180001</v>
+        <v>32.08081044645</v>
       </c>
       <c r="Q54">
-        <v>50.33409704180001</v>
+        <v>50.18081044645</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1957567162288773</v>
+        <v>0.1986981296408528</v>
       </c>
       <c r="T54">
-        <v>1.796442820255314</v>
+        <v>1.831680195000711</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.043970577842682</v>
+        <v>4.948801321656971</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1183007709312008</v>
+        <v>0.1181957180725405</v>
       </c>
       <c r="C55">
-        <v>165.2658591370225</v>
+        <v>162.2411193982936</v>
       </c>
       <c r="D55">
-        <v>288.5025691370225</v>
+        <v>288.7388993982937</v>
       </c>
       <c r="E55">
-        <v>172.82971</v>
+        <v>176.09078</v>
       </c>
       <c r="F55">
-        <v>172.83671</v>
+        <v>176.09778</v>
       </c>
       <c r="G55">
         <v>49.6</v>
@@ -5797,28 +5797,28 @@
         <v>47.3</v>
       </c>
       <c r="M55">
-        <v>9.557870063000001</v>
+        <v>9.738207234000003</v>
       </c>
       <c r="N55">
-        <v>37.742129937</v>
+        <v>37.561792766</v>
       </c>
       <c r="O55">
-        <v>5.66131949055</v>
+        <v>5.634268914900001</v>
       </c>
       <c r="P55">
-        <v>32.08081044645</v>
+        <v>31.9275238511</v>
       </c>
       <c r="Q55">
-        <v>50.18081044645</v>
+        <v>50.0275238511</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1986981296408528</v>
+        <v>0.2017674305924794</v>
       </c>
       <c r="T55">
-        <v>1.831680195000711</v>
+        <v>1.868449629517647</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.948801321656971</v>
+        <v>4.857156852737397</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1181957180725405</v>
+        <v>0.1180906652138802</v>
       </c>
       <c r="C56">
-        <v>162.2411193982936</v>
+        <v>159.2167671623999</v>
       </c>
       <c r="D56">
-        <v>288.7388993982937</v>
+        <v>288.9756171623999</v>
       </c>
       <c r="E56">
-        <v>176.09078</v>
+        <v>179.35185</v>
       </c>
       <c r="F56">
-        <v>176.09778</v>
+        <v>179.35885</v>
       </c>
       <c r="G56">
         <v>49.6</v>
@@ -5879,28 +5879,28 @@
         <v>47.3</v>
       </c>
       <c r="M56">
-        <v>9.738207234000003</v>
+        <v>9.918544405000002</v>
       </c>
       <c r="N56">
-        <v>37.561792766</v>
+        <v>37.38145559500001</v>
       </c>
       <c r="O56">
-        <v>5.634268914900001</v>
+        <v>5.607218339250001</v>
       </c>
       <c r="P56">
-        <v>31.9275238511</v>
+        <v>31.77423725575001</v>
       </c>
       <c r="Q56">
-        <v>50.0275238511</v>
+        <v>49.87423725575</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2017674305924794</v>
+        <v>0.2049731449197338</v>
       </c>
       <c r="T56">
-        <v>1.868449629517647</v>
+        <v>1.906853261124224</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.857156852737397</v>
+        <v>4.768844909960354</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1180906652138802</v>
+        <v>0.1179856123552199</v>
       </c>
       <c r="C57">
-        <v>159.2167671623999</v>
+        <v>156.1928033831862</v>
       </c>
       <c r="D57">
-        <v>288.9756171623999</v>
+        <v>289.2127233831862</v>
       </c>
       <c r="E57">
-        <v>179.35185</v>
+        <v>182.61292</v>
       </c>
       <c r="F57">
-        <v>179.35885</v>
+        <v>182.61992</v>
       </c>
       <c r="G57">
         <v>49.6</v>
@@ -5961,28 +5961,28 @@
         <v>47.3</v>
       </c>
       <c r="M57">
-        <v>9.918544405000002</v>
+        <v>10.098881576</v>
       </c>
       <c r="N57">
-        <v>37.38145559500001</v>
+        <v>37.201118424</v>
       </c>
       <c r="O57">
-        <v>5.607218339250001</v>
+        <v>5.5801677636</v>
       </c>
       <c r="P57">
-        <v>31.77423725575001</v>
+        <v>31.6209506604</v>
       </c>
       <c r="Q57">
-        <v>49.87423725575</v>
+        <v>49.72095066040001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2049731449197338</v>
+        <v>0.2083245735345907</v>
       </c>
       <c r="T57">
-        <v>1.906853261124224</v>
+        <v>1.947002512349282</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.768844909960354</v>
+        <v>4.683686965139633</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1179856123552199</v>
+        <v>0.1178805594965596</v>
       </c>
       <c r="C58">
-        <v>156.1928033831862</v>
+        <v>153.1692290176309</v>
       </c>
       <c r="D58">
-        <v>289.2127233831862</v>
+        <v>289.4502190176309</v>
       </c>
       <c r="E58">
-        <v>182.61292</v>
+        <v>185.87399</v>
       </c>
       <c r="F58">
-        <v>182.61992</v>
+        <v>185.88099</v>
       </c>
       <c r="G58">
         <v>49.6</v>
@@ -6043,28 +6043,28 @@
         <v>47.3</v>
       </c>
       <c r="M58">
-        <v>10.098881576</v>
+        <v>10.279218747</v>
       </c>
       <c r="N58">
-        <v>37.201118424</v>
+        <v>37.020781253</v>
       </c>
       <c r="O58">
-        <v>5.5801677636</v>
+        <v>5.55311718795</v>
       </c>
       <c r="P58">
-        <v>31.6209506604</v>
+        <v>31.46766406505</v>
       </c>
       <c r="Q58">
-        <v>49.72095066040001</v>
+        <v>49.56766406505</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2083245735345907</v>
+        <v>0.2118318825501387</v>
       </c>
       <c r="T58">
-        <v>1.947002512349282</v>
+        <v>1.989019170608064</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.683686965139633</v>
+        <v>4.601517018382798</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1178805594965596</v>
+        <v>0.1177755066378993</v>
       </c>
       <c r="C59">
-        <v>153.1692290176309</v>
+        <v>150.1460450258583</v>
       </c>
       <c r="D59">
-        <v>289.4502190176309</v>
+        <v>289.6881050258583</v>
       </c>
       <c r="E59">
-        <v>185.87399</v>
+        <v>189.13506</v>
       </c>
       <c r="F59">
-        <v>185.88099</v>
+        <v>189.14206</v>
       </c>
       <c r="G59">
         <v>49.6</v>
@@ -6125,28 +6125,28 @@
         <v>47.3</v>
       </c>
       <c r="M59">
-        <v>10.279218747</v>
+        <v>10.459555918</v>
       </c>
       <c r="N59">
-        <v>37.020781253</v>
+        <v>36.840444082</v>
       </c>
       <c r="O59">
-        <v>5.55311718795</v>
+        <v>5.5260666123</v>
       </c>
       <c r="P59">
-        <v>31.46766406505</v>
+        <v>31.31437746970001</v>
       </c>
       <c r="Q59">
-        <v>49.56766406505</v>
+        <v>49.41437746970001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2118318825501387</v>
+        <v>0.2155062062807127</v>
       </c>
       <c r="T59">
-        <v>1.989019170608064</v>
+        <v>2.033036622117263</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.601517018382798</v>
+        <v>4.522180518065852</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1177755066378993</v>
+        <v>0.118924203779239</v>
       </c>
       <c r="C60">
-        <v>150.1460450258583</v>
+        <v>144.3048665203403</v>
       </c>
       <c r="D60">
-        <v>289.6881050258583</v>
+        <v>287.1079965203402</v>
       </c>
       <c r="E60">
-        <v>189.13506</v>
+        <v>192.39613</v>
       </c>
       <c r="F60">
-        <v>189.14206</v>
+        <v>192.40313</v>
       </c>
       <c r="G60">
         <v>49.6</v>
@@ -6207,45 +6207,45 @@
         <v>47.3</v>
       </c>
       <c r="M60">
-        <v>10.459555918</v>
+        <v>11.120900914</v>
       </c>
       <c r="N60">
-        <v>36.840444082</v>
+        <v>36.179099086</v>
       </c>
       <c r="O60">
-        <v>5.5260666123</v>
+        <v>5.4268648629</v>
       </c>
       <c r="P60">
-        <v>31.31437746970001</v>
+        <v>30.7522342231</v>
       </c>
       <c r="Q60">
-        <v>49.41437746970001</v>
+        <v>48.8522342231</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2155062062807127</v>
+        <v>0.2193597653152171</v>
       </c>
       <c r="T60">
-        <v>2.033036622117263</v>
+        <v>2.079201266383009</v>
       </c>
       <c r="U60">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V60">
         <v>0.15</v>
       </c>
       <c r="W60">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>4.522180518065853</v>
+        <v>4.253252534644425</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.118924203779239</v>
+        <v>0.1188404009205787</v>
       </c>
       <c r="C61">
-        <v>144.3048665203403</v>
+        <v>141.2304723856821</v>
       </c>
       <c r="D61">
-        <v>287.1079965203402</v>
+        <v>287.2946723856821</v>
       </c>
       <c r="E61">
-        <v>192.39613</v>
+        <v>195.6572</v>
       </c>
       <c r="F61">
-        <v>192.40313</v>
+        <v>195.6642</v>
       </c>
       <c r="G61">
         <v>49.6</v>
@@ -6289,28 +6289,28 @@
         <v>47.3</v>
       </c>
       <c r="M61">
-        <v>11.120900914</v>
+        <v>11.30939076</v>
       </c>
       <c r="N61">
-        <v>36.179099086</v>
+        <v>35.99060924</v>
       </c>
       <c r="O61">
-        <v>5.4268648629</v>
+        <v>5.398591386</v>
       </c>
       <c r="P61">
-        <v>30.7522342231</v>
+        <v>30.592017854</v>
       </c>
       <c r="Q61">
-        <v>48.8522342231</v>
+        <v>48.692017854</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2193597653152171</v>
+        <v>0.2234060023014468</v>
       </c>
       <c r="T61">
-        <v>2.079201266383009</v>
+        <v>2.127674142862042</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.253252534644425</v>
+        <v>4.18236499240035</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1188404009205787</v>
+        <v>0.1187565980619184</v>
       </c>
       <c r="C62">
-        <v>141.2304723856821</v>
+        <v>138.1563211599763</v>
       </c>
       <c r="D62">
-        <v>287.2946723856821</v>
+        <v>287.4815911599763</v>
       </c>
       <c r="E62">
-        <v>195.6572</v>
+        <v>198.91827</v>
       </c>
       <c r="F62">
-        <v>195.6642</v>
+        <v>198.92527</v>
       </c>
       <c r="G62">
         <v>49.6</v>
@@ -6371,28 +6371,28 @@
         <v>47.3</v>
       </c>
       <c r="M62">
-        <v>11.30939076</v>
+        <v>11.497880606</v>
       </c>
       <c r="N62">
-        <v>35.99060924</v>
+        <v>35.802119394</v>
       </c>
       <c r="O62">
-        <v>5.398591386</v>
+        <v>5.3703179091</v>
       </c>
       <c r="P62">
-        <v>30.592017854</v>
+        <v>30.4318014849</v>
       </c>
       <c r="Q62">
-        <v>48.692017854</v>
+        <v>48.5318014849</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2234060023014468</v>
+        <v>0.2276597386203036</v>
       </c>
       <c r="T62">
-        <v>2.127674142862042</v>
+        <v>2.178632807878462</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.18236499240035</v>
+        <v>4.113801631869197</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1187565980619184</v>
+        <v>0.1186727952032581</v>
       </c>
       <c r="C63">
-        <v>138.1563211599763</v>
+        <v>135.0824133176534</v>
       </c>
       <c r="D63">
-        <v>287.4815911599763</v>
+        <v>287.6687533176535</v>
       </c>
       <c r="E63">
-        <v>198.91827</v>
+        <v>202.17934</v>
       </c>
       <c r="F63">
-        <v>198.92527</v>
+        <v>202.18634</v>
       </c>
       <c r="G63">
         <v>49.6</v>
@@ -6453,28 +6453,28 @@
         <v>47.3</v>
       </c>
       <c r="M63">
-        <v>11.497880606</v>
+        <v>11.686370452</v>
       </c>
       <c r="N63">
-        <v>35.802119394</v>
+        <v>35.61362954800001</v>
       </c>
       <c r="O63">
-        <v>5.3703179091</v>
+        <v>5.342044432200001</v>
       </c>
       <c r="P63">
-        <v>30.4318014849</v>
+        <v>30.2715851158</v>
       </c>
       <c r="Q63">
-        <v>48.5318014849</v>
+        <v>48.3715851158</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2276597386203036</v>
+        <v>0.2321373557980477</v>
       </c>
       <c r="T63">
-        <v>2.178632807878462</v>
+        <v>2.232273507895746</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.113801631869197</v>
+        <v>4.0474499926455</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1186727952032581</v>
+        <v>0.1204632423445978</v>
       </c>
       <c r="C64">
-        <v>135.0824133176534</v>
+        <v>127.8749153112969</v>
       </c>
       <c r="D64">
-        <v>287.6687533176535</v>
+        <v>283.7223253112969</v>
       </c>
       <c r="E64">
-        <v>202.17934</v>
+        <v>205.44041</v>
       </c>
       <c r="F64">
-        <v>202.18634</v>
+        <v>205.44741</v>
       </c>
       <c r="G64">
         <v>49.6</v>
@@ -6535,45 +6535,45 @@
         <v>47.3</v>
       </c>
       <c r="M64">
-        <v>11.686370452</v>
+        <v>12.593926233</v>
       </c>
       <c r="N64">
-        <v>35.61362954800001</v>
+        <v>34.70607376700001</v>
       </c>
       <c r="O64">
-        <v>5.342044432200001</v>
+        <v>5.20591106505</v>
       </c>
       <c r="P64">
-        <v>30.2715851158</v>
+        <v>29.50016270195001</v>
       </c>
       <c r="Q64">
-        <v>48.3715851158</v>
+        <v>47.60016270195001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2321373557980477</v>
+        <v>0.2368570063367509</v>
       </c>
       <c r="T64">
-        <v>2.232273507895746</v>
+        <v>2.288813705211262</v>
       </c>
       <c r="U64">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V64">
         <v>0.15</v>
       </c>
       <c r="W64">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.0474499926455</v>
+        <v>3.755778708315704</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1204632423445978</v>
+        <v>0.1204091894859375</v>
       </c>
       <c r="C65">
-        <v>127.8749153112969</v>
+        <v>124.7314005727711</v>
       </c>
       <c r="D65">
-        <v>283.7223253112969</v>
+        <v>283.8398805727711</v>
       </c>
       <c r="E65">
-        <v>205.44041</v>
+        <v>208.70148</v>
       </c>
       <c r="F65">
-        <v>205.44741</v>
+        <v>208.70848</v>
       </c>
       <c r="G65">
         <v>49.6</v>
@@ -6617,28 +6617,28 @@
         <v>47.3</v>
       </c>
       <c r="M65">
-        <v>12.593926233</v>
+        <v>12.793829824</v>
       </c>
       <c r="N65">
-        <v>34.70607376700001</v>
+        <v>34.506170176</v>
       </c>
       <c r="O65">
-        <v>5.20591106505</v>
+        <v>5.1759255264</v>
       </c>
       <c r="P65">
-        <v>29.50016270195001</v>
+        <v>29.3302446496</v>
       </c>
       <c r="Q65">
-        <v>47.60016270195001</v>
+        <v>47.43024464960001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2368570063367509</v>
+        <v>0.2418388596831599</v>
       </c>
       <c r="T65">
-        <v>2.288813705211262</v>
+        <v>2.348495024599861</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.755778708315704</v>
+        <v>3.697094665998271</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1204091894859375</v>
+        <v>0.1203551366272773</v>
       </c>
       <c r="C66">
-        <v>124.7314005727711</v>
+        <v>121.5879832884559</v>
       </c>
       <c r="D66">
-        <v>283.8398805727711</v>
+        <v>283.9575332884559</v>
       </c>
       <c r="E66">
-        <v>208.70148</v>
+        <v>211.96255</v>
       </c>
       <c r="F66">
-        <v>208.70848</v>
+        <v>211.96955</v>
       </c>
       <c r="G66">
         <v>49.6</v>
@@ -6699,28 +6699,28 @@
         <v>47.3</v>
       </c>
       <c r="M66">
-        <v>12.793829824</v>
+        <v>12.993733415</v>
       </c>
       <c r="N66">
-        <v>34.506170176</v>
+        <v>34.306266585</v>
       </c>
       <c r="O66">
-        <v>5.1759255264</v>
+        <v>5.14593998775</v>
       </c>
       <c r="P66">
-        <v>29.3302446496</v>
+        <v>29.16032659725</v>
       </c>
       <c r="Q66">
-        <v>47.43024464960001</v>
+        <v>47.26032659725</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2418388596831599</v>
+        <v>0.2471053903636493</v>
       </c>
       <c r="T66">
-        <v>2.348495024599861</v>
+        <v>2.411586705096381</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.697094665998271</v>
+        <v>3.640216286521375</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1203551366272773</v>
+        <v>0.120301083768617</v>
       </c>
       <c r="C67">
-        <v>121.5879832884559</v>
+        <v>118.4446635795872</v>
       </c>
       <c r="D67">
-        <v>283.9575332884559</v>
+        <v>284.0752835795872</v>
       </c>
       <c r="E67">
-        <v>211.96255</v>
+        <v>215.22362</v>
       </c>
       <c r="F67">
-        <v>211.96955</v>
+        <v>215.23062</v>
       </c>
       <c r="G67">
         <v>49.6</v>
@@ -6781,28 +6781,28 @@
         <v>47.3</v>
       </c>
       <c r="M67">
-        <v>12.993733415</v>
+        <v>13.193637006</v>
       </c>
       <c r="N67">
-        <v>34.306266585</v>
+        <v>34.106362994</v>
       </c>
       <c r="O67">
-        <v>5.14593998775</v>
+        <v>5.1159544491</v>
       </c>
       <c r="P67">
-        <v>29.16032659725</v>
+        <v>28.9904085449</v>
       </c>
       <c r="Q67">
-        <v>47.26032659725</v>
+        <v>47.0904085449</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2471053903636493</v>
+        <v>0.2526817169665205</v>
       </c>
       <c r="T67">
-        <v>2.411586705096381</v>
+        <v>2.478389660916226</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.640216286521375</v>
+        <v>3.585061494301354</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.120301083768617</v>
+        <v>0.1202470309099567</v>
       </c>
       <c r="C68">
-        <v>118.4446635795872</v>
+        <v>115.3014415676015</v>
       </c>
       <c r="D68">
-        <v>284.0752835795872</v>
+        <v>284.1931315676015</v>
       </c>
       <c r="E68">
-        <v>215.22362</v>
+        <v>218.48469</v>
       </c>
       <c r="F68">
-        <v>215.23062</v>
+        <v>218.49169</v>
       </c>
       <c r="G68">
         <v>49.6</v>
@@ -6863,28 +6863,28 @@
         <v>47.3</v>
       </c>
       <c r="M68">
-        <v>13.193637006</v>
+        <v>13.393540597</v>
       </c>
       <c r="N68">
-        <v>34.106362994</v>
+        <v>33.906459403</v>
       </c>
       <c r="O68">
-        <v>5.1159544491</v>
+        <v>5.08596891045</v>
       </c>
       <c r="P68">
-        <v>28.9904085449</v>
+        <v>28.82049049255</v>
       </c>
       <c r="Q68">
-        <v>47.0904085449</v>
+        <v>46.92049049255</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2526817169665205</v>
+        <v>0.2585960027574445</v>
       </c>
       <c r="T68">
-        <v>2.478389660916226</v>
+        <v>2.549241280725151</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.585061494301354</v>
+        <v>3.531553113789393</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1202470309099567</v>
+        <v>0.1218113780512964</v>
       </c>
       <c r="C69">
-        <v>115.3014415676015</v>
+        <v>108.6687903804448</v>
       </c>
       <c r="D69">
-        <v>284.1931315676015</v>
+        <v>280.8215503804448</v>
       </c>
       <c r="E69">
-        <v>218.48469</v>
+        <v>221.74576</v>
       </c>
       <c r="F69">
-        <v>218.49169</v>
+        <v>221.75276</v>
       </c>
       <c r="G69">
         <v>49.6</v>
@@ -6945,45 +6945,45 @@
         <v>47.3</v>
       </c>
       <c r="M69">
-        <v>13.393540597</v>
+        <v>14.214351916</v>
       </c>
       <c r="N69">
-        <v>33.906459403</v>
+        <v>33.085648084</v>
       </c>
       <c r="O69">
-        <v>5.08596891045</v>
+        <v>4.9628472126</v>
       </c>
       <c r="P69">
-        <v>28.82049049255</v>
+        <v>28.1228008714</v>
       </c>
       <c r="Q69">
-        <v>46.92049049255</v>
+        <v>46.2228008714</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2585960027574445</v>
+        <v>0.2648799314103012</v>
       </c>
       <c r="T69">
-        <v>2.549241280725151</v>
+        <v>2.624521126772135</v>
       </c>
       <c r="U69">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V69">
         <v>0.15</v>
       </c>
       <c r="W69">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y69">
-        <v>3.531553113789393</v>
+        <v>3.327622692861433</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1218113780512964</v>
+        <v>0.1217811251926361</v>
       </c>
       <c r="C70">
-        <v>108.6687903804448</v>
+        <v>105.4721645178258</v>
       </c>
       <c r="D70">
-        <v>280.8215503804448</v>
+        <v>280.8859945178258</v>
       </c>
       <c r="E70">
-        <v>221.74576</v>
+        <v>225.00683</v>
       </c>
       <c r="F70">
-        <v>221.75276</v>
+        <v>225.01383</v>
       </c>
       <c r="G70">
         <v>49.6</v>
@@ -7027,28 +7027,28 @@
         <v>47.3</v>
       </c>
       <c r="M70">
-        <v>14.214351916</v>
+        <v>14.423386503</v>
       </c>
       <c r="N70">
-        <v>33.085648084</v>
+        <v>32.876613497</v>
       </c>
       <c r="O70">
-        <v>4.9628472126</v>
+        <v>4.93149202455</v>
       </c>
       <c r="P70">
-        <v>28.1228008714</v>
+        <v>27.94512147245</v>
       </c>
       <c r="Q70">
-        <v>46.2228008714</v>
+        <v>46.04512147245001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2648799314103012</v>
+        <v>0.2715692748149551</v>
       </c>
       <c r="T70">
-        <v>2.624521126772135</v>
+        <v>2.704657737080215</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.327622692861433</v>
+        <v>3.279396277022862</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1217811251926361</v>
+        <v>0.1217508723339758</v>
       </c>
       <c r="C71">
-        <v>105.4721645178258</v>
+        <v>102.2755682398318</v>
       </c>
       <c r="D71">
-        <v>280.8859945178258</v>
+        <v>280.9504682398318</v>
       </c>
       <c r="E71">
-        <v>225.00683</v>
+        <v>228.2679</v>
       </c>
       <c r="F71">
-        <v>225.01383</v>
+        <v>228.2749</v>
       </c>
       <c r="G71">
         <v>49.6</v>
@@ -7109,28 +7109,28 @@
         <v>47.3</v>
       </c>
       <c r="M71">
-        <v>14.423386503</v>
+        <v>14.63242109</v>
       </c>
       <c r="N71">
-        <v>32.876613497</v>
+        <v>32.66757891</v>
       </c>
       <c r="O71">
-        <v>4.93149202455</v>
+        <v>4.900136836500001</v>
       </c>
       <c r="P71">
-        <v>27.94512147245</v>
+        <v>27.7674420735</v>
       </c>
       <c r="Q71">
-        <v>46.04512147245001</v>
+        <v>45.8674420735</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2715692748149551</v>
+        <v>0.278704574446586</v>
       </c>
       <c r="T71">
-        <v>2.704657737080215</v>
+        <v>2.790136788075499</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.279396277022862</v>
+        <v>3.232547758779678</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1217508723339758</v>
+        <v>0.1217206194753155</v>
       </c>
       <c r="C72">
-        <v>102.2755682398318</v>
+        <v>99.07900156683959</v>
       </c>
       <c r="D72">
-        <v>280.9504682398318</v>
+        <v>281.0149715668396</v>
       </c>
       <c r="E72">
-        <v>228.2679</v>
+        <v>231.52897</v>
       </c>
       <c r="F72">
-        <v>228.2749</v>
+        <v>231.53597</v>
       </c>
       <c r="G72">
         <v>49.6</v>
@@ -7191,28 +7191,28 @@
         <v>47.3</v>
       </c>
       <c r="M72">
-        <v>14.63242109</v>
+        <v>14.841455677</v>
       </c>
       <c r="N72">
-        <v>32.66757891</v>
+        <v>32.458544323</v>
       </c>
       <c r="O72">
-        <v>4.900136836500001</v>
+        <v>4.86878164845</v>
       </c>
       <c r="P72">
-        <v>27.7674420735</v>
+        <v>27.58976267455</v>
       </c>
       <c r="Q72">
-        <v>45.8674420735</v>
+        <v>45.68976267455</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.278704574446586</v>
+        <v>0.2863319637079845</v>
       </c>
       <c r="T72">
-        <v>2.790136788075499</v>
+        <v>2.881510946035977</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.232547758779678</v>
+        <v>3.187018917106724</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1217206194753155</v>
+        <v>0.1216903666166552</v>
       </c>
       <c r="C73">
-        <v>99.07900156683962</v>
+        <v>95.88246451924513</v>
       </c>
       <c r="D73">
-        <v>281.0149715668396</v>
+        <v>281.0795045192451</v>
       </c>
       <c r="E73">
-        <v>231.52897</v>
+        <v>234.79004</v>
       </c>
       <c r="F73">
-        <v>231.53597</v>
+        <v>234.79704</v>
       </c>
       <c r="G73">
         <v>49.6</v>
@@ -7273,28 +7273,28 @@
         <v>47.3</v>
       </c>
       <c r="M73">
-        <v>14.841455677</v>
+        <v>15.050490264</v>
       </c>
       <c r="N73">
-        <v>32.458544323</v>
+        <v>32.249509736</v>
       </c>
       <c r="O73">
-        <v>4.86878164845</v>
+        <v>4.8374264604</v>
       </c>
       <c r="P73">
-        <v>27.58976267455</v>
+        <v>27.4120832756</v>
       </c>
       <c r="Q73">
-        <v>45.68976267455</v>
+        <v>45.51208327560001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2863319637079844</v>
+        <v>0.2945041664880542</v>
       </c>
       <c r="T73">
-        <v>2.881510946035975</v>
+        <v>2.979411829565058</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.187018917106725</v>
+        <v>3.142754765480243</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1216903666166552</v>
+        <v>0.1216601137579949</v>
       </c>
       <c r="C74">
-        <v>95.88246451924513</v>
+        <v>92.68595711746255</v>
       </c>
       <c r="D74">
-        <v>281.0795045192451</v>
+        <v>281.1440671174626</v>
       </c>
       <c r="E74">
-        <v>234.79004</v>
+        <v>238.05111</v>
       </c>
       <c r="F74">
-        <v>234.79704</v>
+        <v>238.05811</v>
       </c>
       <c r="G74">
         <v>49.6</v>
@@ -7355,28 +7355,28 @@
         <v>47.3</v>
       </c>
       <c r="M74">
-        <v>15.050490264</v>
+        <v>15.259524851</v>
       </c>
       <c r="N74">
-        <v>32.249509736</v>
+        <v>32.040475149</v>
       </c>
       <c r="O74">
-        <v>4.8374264604</v>
+        <v>4.806071272350001</v>
       </c>
       <c r="P74">
-        <v>27.4120832756</v>
+        <v>27.23440387665</v>
       </c>
       <c r="Q74">
-        <v>45.51208327560001</v>
+        <v>45.33440387665</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2945041664880542</v>
+        <v>0.3032817176222033</v>
       </c>
       <c r="T74">
-        <v>2.979411829565058</v>
+        <v>3.08456463039259</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.142754765480243</v>
+        <v>3.099703330336678</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1216601137579949</v>
+        <v>0.1216298608993346</v>
       </c>
       <c r="C75">
-        <v>92.68595711746255</v>
+        <v>89.48947938192526</v>
       </c>
       <c r="D75">
-        <v>281.1440671174626</v>
+        <v>281.2086593819253</v>
       </c>
       <c r="E75">
-        <v>238.05111</v>
+        <v>241.31218</v>
       </c>
       <c r="F75">
-        <v>238.05811</v>
+        <v>241.31918</v>
       </c>
       <c r="G75">
         <v>49.6</v>
@@ -7437,28 +7437,28 @@
         <v>47.3</v>
       </c>
       <c r="M75">
-        <v>15.259524851</v>
+        <v>15.468559438</v>
       </c>
       <c r="N75">
-        <v>32.040475149</v>
+        <v>31.831440562</v>
       </c>
       <c r="O75">
-        <v>4.806071272350001</v>
+        <v>4.7747160843</v>
       </c>
       <c r="P75">
-        <v>27.23440387665</v>
+        <v>27.0567244777</v>
       </c>
       <c r="Q75">
-        <v>45.33440387665</v>
+        <v>45.15672447770001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3032817176222033</v>
+        <v>0.3127344649974408</v>
       </c>
       <c r="T75">
-        <v>3.08456463039259</v>
+        <v>3.197806108206857</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.099703330336678</v>
+        <v>3.057815447494291</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1216298608993346</v>
+        <v>0.1215996080406743</v>
       </c>
       <c r="C76">
-        <v>89.48947938192526</v>
+        <v>86.29303133308514</v>
       </c>
       <c r="D76">
-        <v>281.2086593819253</v>
+        <v>281.2732813330852</v>
       </c>
       <c r="E76">
-        <v>241.31218</v>
+        <v>244.57325</v>
       </c>
       <c r="F76">
-        <v>241.31918</v>
+        <v>244.58025</v>
       </c>
       <c r="G76">
         <v>49.6</v>
@@ -7519,28 +7519,28 @@
         <v>47.3</v>
       </c>
       <c r="M76">
-        <v>15.468559438</v>
+        <v>15.677594025</v>
       </c>
       <c r="N76">
-        <v>31.831440562</v>
+        <v>31.622405975</v>
       </c>
       <c r="O76">
-        <v>4.7747160843</v>
+        <v>4.74336089625</v>
       </c>
       <c r="P76">
-        <v>27.0567244777</v>
+        <v>26.87904507875</v>
       </c>
       <c r="Q76">
-        <v>45.15672447770001</v>
+        <v>44.97904507875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3127344649974408</v>
+        <v>0.3229434321626973</v>
       </c>
       <c r="T76">
-        <v>3.197806108206857</v>
+        <v>3.320106904246264</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.057815447494291</v>
+        <v>3.017044574861033</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1215996080406743</v>
+        <v>0.126608155182014</v>
       </c>
       <c r="C77">
-        <v>86.29303133308514</v>
+        <v>72.72313900558825</v>
       </c>
       <c r="D77">
-        <v>281.2732813330852</v>
+        <v>270.9644590055883</v>
       </c>
       <c r="E77">
-        <v>244.57325</v>
+        <v>247.83432</v>
       </c>
       <c r="F77">
-        <v>244.58025</v>
+        <v>247.84132</v>
       </c>
       <c r="G77">
         <v>49.6</v>
@@ -7601,45 +7601,45 @@
         <v>47.3</v>
       </c>
       <c r="M77">
-        <v>15.677594025</v>
+        <v>17.819790908</v>
       </c>
       <c r="N77">
-        <v>31.622405975</v>
+        <v>29.480209092</v>
       </c>
       <c r="O77">
-        <v>4.74336089625</v>
+        <v>4.4220313638</v>
       </c>
       <c r="P77">
-        <v>26.87904507875</v>
+        <v>25.0581777282</v>
       </c>
       <c r="Q77">
-        <v>44.97904507875</v>
+        <v>43.1581777282</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3229434321626973</v>
+        <v>0.3340031465917251</v>
       </c>
       <c r="T77">
-        <v>3.320106904246264</v>
+        <v>3.452599433288956</v>
       </c>
       <c r="U77">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V77">
         <v>0.15</v>
       </c>
       <c r="W77">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>3.017044574861033</v>
+        <v>2.654352132648492</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.126608155182014</v>
+        <v>0.1266442023233537</v>
       </c>
       <c r="C78">
-        <v>72.72313900558825</v>
+        <v>69.39061321534871</v>
       </c>
       <c r="D78">
-        <v>270.9644590055883</v>
+        <v>270.8930032153487</v>
       </c>
       <c r="E78">
-        <v>247.83432</v>
+        <v>251.09539</v>
       </c>
       <c r="F78">
-        <v>247.84132</v>
+        <v>251.10239</v>
       </c>
       <c r="G78">
         <v>49.6</v>
@@ -7683,28 +7683,28 @@
         <v>47.3</v>
       </c>
       <c r="M78">
-        <v>17.819790908</v>
+        <v>18.054261841</v>
       </c>
       <c r="N78">
-        <v>29.480209092</v>
+        <v>29.245738159</v>
       </c>
       <c r="O78">
-        <v>4.4220313638</v>
+        <v>4.38686072385</v>
       </c>
       <c r="P78">
-        <v>25.0581777282</v>
+        <v>24.85887743515</v>
       </c>
       <c r="Q78">
-        <v>43.1581777282</v>
+        <v>42.95887743515</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3340031465917251</v>
+        <v>0.3460245753189292</v>
       </c>
       <c r="T78">
-        <v>3.452599433288956</v>
+        <v>3.59661305181362</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.654352132648492</v>
+        <v>2.61988002702968</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1266442023233537</v>
+        <v>0.1266802494646934</v>
       </c>
       <c r="C79">
-        <v>69.39061321534871</v>
+        <v>66.05812510225593</v>
       </c>
       <c r="D79">
-        <v>270.8930032153487</v>
+        <v>270.8215851022559</v>
       </c>
       <c r="E79">
-        <v>251.09539</v>
+        <v>254.35646</v>
       </c>
       <c r="F79">
-        <v>251.10239</v>
+        <v>254.36346</v>
       </c>
       <c r="G79">
         <v>49.6</v>
@@ -7765,28 +7765,28 @@
         <v>47.3</v>
       </c>
       <c r="M79">
-        <v>18.054261841</v>
+        <v>18.288732774</v>
       </c>
       <c r="N79">
-        <v>29.245738159</v>
+        <v>29.011267226</v>
       </c>
       <c r="O79">
-        <v>4.38686072385</v>
+        <v>4.3516900839</v>
       </c>
       <c r="P79">
-        <v>24.85887743515</v>
+        <v>24.6595771421</v>
       </c>
       <c r="Q79">
-        <v>42.95887743515</v>
+        <v>42.7595771421</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3460245753189292</v>
+        <v>0.359138861203152</v>
       </c>
       <c r="T79">
-        <v>3.59661305181362</v>
+        <v>3.75371881747689</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.61988002702968</v>
+        <v>2.58629182155494</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1266802494646934</v>
+        <v>0.1267162966060331</v>
       </c>
       <c r="C80">
-        <v>66.05812510225593</v>
+        <v>62.72567463651802</v>
       </c>
       <c r="D80">
-        <v>270.8215851022559</v>
+        <v>270.750204636518</v>
       </c>
       <c r="E80">
-        <v>254.35646</v>
+        <v>257.61753</v>
       </c>
       <c r="F80">
-        <v>254.36346</v>
+        <v>257.62453</v>
       </c>
       <c r="G80">
         <v>49.6</v>
@@ -7847,28 +7847,28 @@
         <v>47.3</v>
       </c>
       <c r="M80">
-        <v>18.288732774</v>
+        <v>18.523203707</v>
       </c>
       <c r="N80">
-        <v>29.011267226</v>
+        <v>28.776796293</v>
       </c>
       <c r="O80">
-        <v>4.3516900839</v>
+        <v>4.31651944395</v>
       </c>
       <c r="P80">
-        <v>24.6595771421</v>
+        <v>24.46027684905</v>
       </c>
       <c r="Q80">
-        <v>42.7595771421</v>
+        <v>42.56027684905</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.359138861203152</v>
+        <v>0.3735021266953959</v>
       </c>
       <c r="T80">
-        <v>3.75371881747689</v>
+        <v>3.925787037012853</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.58629182155494</v>
+        <v>2.553553950396017</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1267162966060331</v>
+        <v>0.1267523437473728</v>
       </c>
       <c r="C81">
-        <v>62.72567463651802</v>
+        <v>59.3932617883749</v>
       </c>
       <c r="D81">
-        <v>270.750204636518</v>
+        <v>270.6788617883749</v>
       </c>
       <c r="E81">
-        <v>257.61753</v>
+        <v>260.8786</v>
       </c>
       <c r="F81">
-        <v>257.62453</v>
+        <v>260.8856</v>
       </c>
       <c r="G81">
         <v>49.6</v>
@@ -7929,28 +7929,28 @@
         <v>47.3</v>
       </c>
       <c r="M81">
-        <v>18.523203707</v>
+        <v>18.75767464</v>
       </c>
       <c r="N81">
-        <v>28.776796293</v>
+        <v>28.54232536</v>
       </c>
       <c r="O81">
-        <v>4.31651944395</v>
+        <v>4.281348804</v>
       </c>
       <c r="P81">
-        <v>24.46027684905</v>
+        <v>24.260976556</v>
       </c>
       <c r="Q81">
-        <v>42.56027684905</v>
+        <v>42.360976556</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3735021266953959</v>
+        <v>0.3893017187368643</v>
       </c>
       <c r="T81">
-        <v>3.925787037012853</v>
+        <v>4.115062078502413</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.553553950396017</v>
+        <v>2.521634526016067</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1267523437473728</v>
+        <v>0.1294735408887125</v>
       </c>
       <c r="C82">
-        <v>59.3932617883749</v>
+        <v>50.85295512550789</v>
       </c>
       <c r="D82">
-        <v>270.6788617883749</v>
+        <v>265.3996251255079</v>
       </c>
       <c r="E82">
-        <v>260.8786</v>
+        <v>264.13967</v>
       </c>
       <c r="F82">
-        <v>260.8856</v>
+        <v>264.14667</v>
       </c>
       <c r="G82">
         <v>49.6</v>
@@ -8011,45 +8011,45 @@
         <v>47.3</v>
       </c>
       <c r="M82">
-        <v>18.75767464</v>
+        <v>20.022317586</v>
       </c>
       <c r="N82">
-        <v>28.54232536</v>
+        <v>27.277682414</v>
       </c>
       <c r="O82">
-        <v>4.281348804</v>
+        <v>4.0916523621</v>
       </c>
       <c r="P82">
-        <v>24.260976556</v>
+        <v>23.1860300519</v>
       </c>
       <c r="Q82">
-        <v>42.360976556</v>
+        <v>41.2860300519</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3893017187368643</v>
+        <v>0.4067644257300662</v>
       </c>
       <c r="T82">
-        <v>4.115062078502413</v>
+        <v>4.324260808569821</v>
       </c>
       <c r="U82">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V82">
         <v>0.15</v>
       </c>
       <c r="W82">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.521634526016067</v>
+        <v>2.362363887039385</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1294735408887125</v>
+        <v>0.1295427380300522</v>
       </c>
       <c r="C83">
-        <v>50.85295512550789</v>
+        <v>47.46032329613212</v>
       </c>
       <c r="D83">
-        <v>265.3996251255079</v>
+        <v>265.2680632961321</v>
       </c>
       <c r="E83">
-        <v>264.13967</v>
+        <v>267.40074</v>
       </c>
       <c r="F83">
-        <v>264.14667</v>
+        <v>267.40774</v>
       </c>
       <c r="G83">
         <v>49.6</v>
@@ -8093,28 +8093,28 @@
         <v>47.3</v>
       </c>
       <c r="M83">
-        <v>20.022317586</v>
+        <v>20.269506692</v>
       </c>
       <c r="N83">
-        <v>27.277682414</v>
+        <v>27.030493308</v>
       </c>
       <c r="O83">
-        <v>4.0916523621</v>
+        <v>4.0545739962</v>
       </c>
       <c r="P83">
-        <v>23.1860300519</v>
+        <v>22.9759193118</v>
       </c>
       <c r="Q83">
-        <v>41.2860300519</v>
+        <v>41.0759193118</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4067644257300662</v>
+        <v>0.4261674335002903</v>
       </c>
       <c r="T83">
-        <v>4.324260808569821</v>
+        <v>4.556703841978051</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.362363887039385</v>
+        <v>2.333554571343782</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1295427380300522</v>
+        <v>0.129611935171392</v>
       </c>
       <c r="C84">
-        <v>47.46032329613212</v>
+        <v>44.06782183573591</v>
       </c>
       <c r="D84">
-        <v>265.2680632961321</v>
+        <v>265.136631835736</v>
       </c>
       <c r="E84">
-        <v>267.40074</v>
+        <v>270.6618100000001</v>
       </c>
       <c r="F84">
-        <v>267.40774</v>
+        <v>270.6688100000001</v>
       </c>
       <c r="G84">
         <v>49.6</v>
@@ -8175,28 +8175,28 @@
         <v>47.3</v>
       </c>
       <c r="M84">
-        <v>20.269506692</v>
+        <v>20.51669579800001</v>
       </c>
       <c r="N84">
-        <v>27.030493308</v>
+        <v>26.783304202</v>
       </c>
       <c r="O84">
-        <v>4.0545739962</v>
+        <v>4.017495630299999</v>
       </c>
       <c r="P84">
-        <v>22.9759193118</v>
+        <v>22.7658085717</v>
       </c>
       <c r="Q84">
-        <v>41.0759193118</v>
+        <v>40.8658085717</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4261674335002903</v>
+        <v>0.4478531480670117</v>
       </c>
       <c r="T84">
-        <v>4.556703841978051</v>
+        <v>4.81649311461078</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.333554571343782</v>
+        <v>2.305439456026387</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.129611935171392</v>
+        <v>0.1296811323127317</v>
       </c>
       <c r="C85">
-        <v>44.06782183573591</v>
+        <v>40.67545055063488</v>
       </c>
       <c r="D85">
-        <v>265.136631835736</v>
+        <v>265.0053305506349</v>
       </c>
       <c r="E85">
-        <v>270.6618100000001</v>
+        <v>273.92288</v>
       </c>
       <c r="F85">
-        <v>270.6688100000001</v>
+        <v>273.92988</v>
       </c>
       <c r="G85">
         <v>49.6</v>
@@ -8257,28 +8257,28 @@
         <v>47.3</v>
       </c>
       <c r="M85">
-        <v>20.51669579800001</v>
+        <v>20.763884904</v>
       </c>
       <c r="N85">
-        <v>26.783304202</v>
+        <v>26.536115096</v>
       </c>
       <c r="O85">
-        <v>4.017495630299999</v>
+        <v>3.9804172644</v>
       </c>
       <c r="P85">
-        <v>22.7658085717</v>
+        <v>22.5556978316</v>
       </c>
       <c r="Q85">
-        <v>40.8658085717</v>
+        <v>40.6556978316</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4478531480670117</v>
+        <v>0.4722495769545731</v>
       </c>
       <c r="T85">
-        <v>4.81649311461078</v>
+        <v>5.1087560463226</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.305439456026387</v>
+        <v>2.27799374821655</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1296811323127317</v>
+        <v>0.1297503294540714</v>
       </c>
       <c r="C86">
-        <v>40.67545055063488</v>
+        <v>37.28320924752802</v>
       </c>
       <c r="D86">
-        <v>265.0053305506349</v>
+        <v>264.874159247528</v>
       </c>
       <c r="E86">
-        <v>273.92288</v>
+        <v>277.18395</v>
       </c>
       <c r="F86">
-        <v>273.92988</v>
+        <v>277.19095</v>
       </c>
       <c r="G86">
         <v>49.6</v>
@@ -8339,28 +8339,28 @@
         <v>47.3</v>
       </c>
       <c r="M86">
-        <v>20.763884904</v>
+        <v>21.01107401000001</v>
       </c>
       <c r="N86">
-        <v>26.536115096</v>
+        <v>26.28892599</v>
       </c>
       <c r="O86">
-        <v>3.9804172644</v>
+        <v>3.9433388985</v>
       </c>
       <c r="P86">
-        <v>22.5556978316</v>
+        <v>22.3455870915</v>
       </c>
       <c r="Q86">
-        <v>40.6556978316</v>
+        <v>40.4455870915</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4722495769545728</v>
+        <v>0.4998988630271424</v>
       </c>
       <c r="T86">
-        <v>5.108756046322596</v>
+        <v>5.439987368929325</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.27799374821655</v>
+        <v>2.251193821766943</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1297503294540714</v>
+        <v>0.1298195265954111</v>
       </c>
       <c r="C87">
-        <v>37.28320924752802</v>
+        <v>33.89109773349696</v>
       </c>
       <c r="D87">
-        <v>264.874159247528</v>
+        <v>264.7431177334969</v>
       </c>
       <c r="E87">
-        <v>277.18395</v>
+        <v>280.44502</v>
       </c>
       <c r="F87">
-        <v>277.19095</v>
+        <v>280.45202</v>
       </c>
       <c r="G87">
         <v>49.6</v>
@@ -8421,28 +8421,28 @@
         <v>47.3</v>
       </c>
       <c r="M87">
-        <v>21.01107401000001</v>
+        <v>21.258263116</v>
       </c>
       <c r="N87">
-        <v>26.28892599</v>
+        <v>26.041736884</v>
       </c>
       <c r="O87">
-        <v>3.9433388985</v>
+        <v>3.9062605326</v>
       </c>
       <c r="P87">
-        <v>22.3455870915</v>
+        <v>22.1354763514</v>
       </c>
       <c r="Q87">
-        <v>40.4455870915</v>
+        <v>40.2354763514</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4998988630271424</v>
+        <v>0.531498047110079</v>
       </c>
       <c r="T87">
-        <v>5.439987368929325</v>
+        <v>5.818537451908442</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.251193821766943</v>
+        <v>2.225017149420816</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1298195265954111</v>
+        <v>0.1298887237367508</v>
       </c>
       <c r="C88">
-        <v>33.89109773349696</v>
+        <v>30.49911581600475</v>
       </c>
       <c r="D88">
-        <v>264.7431177334969</v>
+        <v>264.6122058160047</v>
       </c>
       <c r="E88">
-        <v>280.44502</v>
+        <v>283.70609</v>
       </c>
       <c r="F88">
-        <v>280.45202</v>
+        <v>283.71309</v>
       </c>
       <c r="G88">
         <v>49.6</v>
@@ -8503,28 +8503,28 @@
         <v>47.3</v>
       </c>
       <c r="M88">
-        <v>21.258263116</v>
+        <v>21.505452222</v>
       </c>
       <c r="N88">
-        <v>26.041736884</v>
+        <v>25.794547778</v>
       </c>
       <c r="O88">
-        <v>3.9062605326</v>
+        <v>3.8691821667</v>
       </c>
       <c r="P88">
-        <v>22.1354763514</v>
+        <v>21.9253656113</v>
       </c>
       <c r="Q88">
-        <v>40.2354763514</v>
+        <v>40.0253656113</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.531498047110079</v>
+        <v>0.567958644128852</v>
       </c>
       <c r="T88">
-        <v>5.818537451908442</v>
+        <v>6.25532600919204</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.225017149420816</v>
+        <v>2.199442239657358</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1298887237367508</v>
+        <v>0.1299579208780905</v>
       </c>
       <c r="C89">
-        <v>30.49911581600475</v>
+        <v>27.10726330289509</v>
       </c>
       <c r="D89">
-        <v>264.6122058160047</v>
+        <v>264.4814233028951</v>
       </c>
       <c r="E89">
-        <v>283.70609</v>
+        <v>286.96716</v>
       </c>
       <c r="F89">
-        <v>283.71309</v>
+        <v>286.97416</v>
       </c>
       <c r="G89">
         <v>49.6</v>
@@ -8585,28 +8585,28 @@
         <v>47.3</v>
       </c>
       <c r="M89">
-        <v>21.505452222</v>
+        <v>21.75264132800001</v>
       </c>
       <c r="N89">
-        <v>25.794547778</v>
+        <v>25.547358672</v>
       </c>
       <c r="O89">
-        <v>3.8691821667</v>
+        <v>3.8321038008</v>
       </c>
       <c r="P89">
-        <v>21.9253656113</v>
+        <v>21.7152548712</v>
       </c>
       <c r="Q89">
-        <v>40.0253656113</v>
+        <v>39.8152548712</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.567958644128852</v>
+        <v>0.6104960073174206</v>
       </c>
       <c r="T89">
-        <v>6.25532600919204</v>
+        <v>6.764912659356238</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.199442239657358</v>
+        <v>2.17444857784307</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1299579208780905</v>
+        <v>0.1300271180194302</v>
       </c>
       <c r="C90">
-        <v>27.10726330289509</v>
+        <v>23.71554000239161</v>
       </c>
       <c r="D90">
-        <v>264.4814233028951</v>
+        <v>264.3507700023916</v>
       </c>
       <c r="E90">
-        <v>286.96716</v>
+        <v>290.22823</v>
       </c>
       <c r="F90">
-        <v>286.97416</v>
+        <v>290.23523</v>
       </c>
       <c r="G90">
         <v>49.6</v>
@@ -8667,28 +8667,28 @@
         <v>47.3</v>
       </c>
       <c r="M90">
-        <v>21.75264132800001</v>
+        <v>21.999830434</v>
       </c>
       <c r="N90">
-        <v>25.547358672</v>
+        <v>25.300169566</v>
       </c>
       <c r="O90">
-        <v>3.8321038008</v>
+        <v>3.7950254349</v>
       </c>
       <c r="P90">
-        <v>21.7152548712</v>
+        <v>21.5051441311</v>
       </c>
       <c r="Q90">
-        <v>39.8152548712</v>
+        <v>39.6051441311</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6104960073174206</v>
+        <v>0.6607674365402744</v>
       </c>
       <c r="T90">
-        <v>6.764912659356238</v>
+        <v>7.367151427732107</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.17444857784307</v>
+        <v>2.150016571350451</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1300271180194302</v>
+        <v>0.1300963151607699</v>
       </c>
       <c r="C91">
-        <v>23.71554000239161</v>
+        <v>20.32394572309641</v>
       </c>
       <c r="D91">
-        <v>264.3507700023916</v>
+        <v>264.2202457230964</v>
       </c>
       <c r="E91">
-        <v>290.22823</v>
+        <v>293.4893</v>
       </c>
       <c r="F91">
-        <v>290.23523</v>
+        <v>293.4963</v>
       </c>
       <c r="G91">
         <v>49.6</v>
@@ -8749,28 +8749,28 @@
         <v>47.3</v>
       </c>
       <c r="M91">
-        <v>21.999830434</v>
+        <v>22.24701954</v>
       </c>
       <c r="N91">
-        <v>25.300169566</v>
+        <v>25.05298046</v>
       </c>
       <c r="O91">
-        <v>3.7950254349</v>
+        <v>3.757947069</v>
       </c>
       <c r="P91">
-        <v>21.5051441311</v>
+        <v>21.295033391</v>
       </c>
       <c r="Q91">
-        <v>39.6051441311</v>
+        <v>39.395033391</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6607674365402744</v>
+        <v>0.721093151607699</v>
       </c>
       <c r="T91">
-        <v>7.367151427732107</v>
+        <v>8.089837949783153</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.150016571350451</v>
+        <v>2.126127498335447</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1300963151607699</v>
+        <v>0.1301655123021096</v>
       </c>
       <c r="C92">
-        <v>20.32394572309641</v>
+        <v>16.9324802739896</v>
       </c>
       <c r="D92">
-        <v>264.2202457230964</v>
+        <v>264.0898502739896</v>
       </c>
       <c r="E92">
-        <v>293.4893</v>
+        <v>296.75037</v>
       </c>
       <c r="F92">
-        <v>293.4963</v>
+        <v>296.75737</v>
       </c>
       <c r="G92">
         <v>49.6</v>
@@ -8831,28 +8831,28 @@
         <v>47.3</v>
       </c>
       <c r="M92">
-        <v>22.24701954</v>
+        <v>22.494208646</v>
       </c>
       <c r="N92">
-        <v>25.05298046</v>
+        <v>24.805791354</v>
       </c>
       <c r="O92">
-        <v>3.757947069</v>
+        <v>3.7208687031</v>
       </c>
       <c r="P92">
-        <v>21.295033391</v>
+        <v>21.0849226509</v>
       </c>
       <c r="Q92">
-        <v>39.395033391</v>
+        <v>39.18492265090001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.721093151607699</v>
+        <v>0.7948245811345512</v>
       </c>
       <c r="T92">
-        <v>8.089837949783153</v>
+        <v>8.973121476734429</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.126127498335447</v>
+        <v>2.1027634598922</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1301655123021096</v>
+        <v>0.1302347094434493</v>
       </c>
       <c r="C93">
-        <v>16.9324802739896</v>
+        <v>13.54114346442822</v>
       </c>
       <c r="D93">
-        <v>264.0898502739896</v>
+        <v>263.9595834644282</v>
       </c>
       <c r="E93">
-        <v>296.75037</v>
+        <v>300.0114400000001</v>
       </c>
       <c r="F93">
-        <v>296.75737</v>
+        <v>300.0184400000001</v>
       </c>
       <c r="G93">
         <v>49.6</v>
@@ -8913,28 +8913,28 @@
         <v>47.3</v>
       </c>
       <c r="M93">
-        <v>22.494208646</v>
+        <v>22.741397752</v>
       </c>
       <c r="N93">
-        <v>24.805791354</v>
+        <v>24.558602248</v>
       </c>
       <c r="O93">
-        <v>3.7208687031</v>
+        <v>3.6837903372</v>
       </c>
       <c r="P93">
-        <v>21.0849226509</v>
+        <v>20.8748119108</v>
       </c>
       <c r="Q93">
-        <v>39.18492265090001</v>
+        <v>38.9748119108</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7948245811345512</v>
+        <v>0.8869888680431166</v>
       </c>
       <c r="T93">
-        <v>8.973121476734429</v>
+        <v>10.07722588542353</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.1027634598922</v>
+        <v>2.079907335328154</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1302347094434493</v>
+        <v>0.130303906584789</v>
       </c>
       <c r="C94">
-        <v>13.54114346442822</v>
+        <v>10.14993510414507</v>
       </c>
       <c r="D94">
-        <v>263.9595834644282</v>
+        <v>263.8294451041451</v>
       </c>
       <c r="E94">
-        <v>300.0114400000001</v>
+        <v>303.27251</v>
       </c>
       <c r="F94">
-        <v>300.0184400000001</v>
+        <v>303.27951</v>
       </c>
       <c r="G94">
         <v>49.6</v>
@@ -8995,28 +8995,28 @@
         <v>47.3</v>
       </c>
       <c r="M94">
-        <v>22.741397752</v>
+        <v>22.988586858</v>
       </c>
       <c r="N94">
-        <v>24.558602248</v>
+        <v>24.311413142</v>
       </c>
       <c r="O94">
-        <v>3.6837903372</v>
+        <v>3.6467119713</v>
       </c>
       <c r="P94">
-        <v>20.8748119108</v>
+        <v>20.6647011707</v>
       </c>
       <c r="Q94">
-        <v>38.9748119108</v>
+        <v>38.76470117070001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8869888680431166</v>
+        <v>1.005485808354129</v>
       </c>
       <c r="T94">
-        <v>10.07722588542353</v>
+        <v>11.49678869659522</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.079907335328154</v>
+        <v>2.057542740324626</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.130303906584789</v>
+        <v>0.1303731037261287</v>
       </c>
       <c r="C95">
-        <v>10.14993510414507</v>
+        <v>6.758855003248186</v>
       </c>
       <c r="D95">
-        <v>263.8294451041451</v>
+        <v>263.6994350032482</v>
       </c>
       <c r="E95">
-        <v>303.27251</v>
+        <v>306.53358</v>
       </c>
       <c r="F95">
-        <v>303.27951</v>
+        <v>306.54058</v>
       </c>
       <c r="G95">
         <v>49.6</v>
@@ -9077,28 +9077,28 @@
         <v>47.3</v>
       </c>
       <c r="M95">
-        <v>22.988586858</v>
+        <v>23.23577596400001</v>
       </c>
       <c r="N95">
-        <v>24.311413142</v>
+        <v>24.064224036</v>
       </c>
       <c r="O95">
-        <v>3.6467119713</v>
+        <v>3.6096336054</v>
       </c>
       <c r="P95">
-        <v>20.6647011707</v>
+        <v>20.4545904306</v>
       </c>
       <c r="Q95">
-        <v>38.76470117070001</v>
+        <v>38.5545904306</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.005485808354129</v>
+        <v>1.163481728768813</v>
       </c>
       <c r="T95">
-        <v>11.49678869659522</v>
+        <v>13.38953911149081</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.057542740324626</v>
+        <v>2.035653987767981</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1303731037261287</v>
+        <v>0.1304423008674684</v>
       </c>
       <c r="C96">
-        <v>6.758855003248186</v>
+        <v>3.367902972219611</v>
       </c>
       <c r="D96">
-        <v>263.6994350032482</v>
+        <v>263.5695529722196</v>
       </c>
       <c r="E96">
-        <v>306.53358</v>
+        <v>309.79465</v>
       </c>
       <c r="F96">
-        <v>306.54058</v>
+        <v>309.8016500000001</v>
       </c>
       <c r="G96">
         <v>49.6</v>
@@ -9159,28 +9159,28 @@
         <v>47.3</v>
       </c>
       <c r="M96">
-        <v>23.23577596400001</v>
+        <v>23.48296507000001</v>
       </c>
       <c r="N96">
-        <v>24.064224036</v>
+        <v>23.81703493</v>
       </c>
       <c r="O96">
-        <v>3.6096336054</v>
+        <v>3.5725552395</v>
       </c>
       <c r="P96">
-        <v>20.4545904306</v>
+        <v>20.2444796905</v>
       </c>
       <c r="Q96">
-        <v>38.5545904306</v>
+        <v>38.3444796905</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.163481728768813</v>
+        <v>1.38467601734937</v>
       </c>
       <c r="T96">
-        <v>13.38953911149081</v>
+        <v>16.03938969234465</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.035653987767981</v>
+        <v>2.014226051054633</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1304423008674684</v>
+        <v>0.1420986980088081</v>
       </c>
       <c r="C97">
-        <v>3.367902972219611</v>
+        <v>-20.08590705864981</v>
       </c>
       <c r="D97">
-        <v>263.5695529722196</v>
+        <v>243.3768129413502</v>
       </c>
       <c r="E97">
-        <v>309.79465</v>
+        <v>313.0557200000001</v>
       </c>
       <c r="F97">
-        <v>309.8016500000001</v>
+        <v>313.0627200000001</v>
       </c>
       <c r="G97">
         <v>49.6</v>
@@ -9241,45 +9241,45 @@
         <v>47.3</v>
       </c>
       <c r="M97">
-        <v>23.48296507000001</v>
+        <v>28.1756448</v>
       </c>
       <c r="N97">
-        <v>23.81703493</v>
+        <v>19.1243552</v>
       </c>
       <c r="O97">
-        <v>3.5725552395</v>
+        <v>2.86865328</v>
       </c>
       <c r="P97">
-        <v>20.2444796905</v>
+        <v>16.25570192</v>
       </c>
       <c r="Q97">
-        <v>38.3444796905</v>
+        <v>34.35570192</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.38467601734937</v>
+        <v>1.716467450220206</v>
       </c>
       <c r="T97">
-        <v>16.03938969234465</v>
+        <v>20.0141655636254</v>
       </c>
       <c r="U97">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V97">
         <v>0.15</v>
       </c>
       <c r="W97">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y97">
-        <v>2.014226051054633</v>
+        <v>1.678754837227363</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1420986980088081</v>
+        <v>0.1422885951501478</v>
       </c>
       <c r="C98">
-        <v>-20.08590705864975</v>
+        <v>-23.65036030498186</v>
       </c>
       <c r="D98">
-        <v>243.3768129413502</v>
+        <v>243.0734296950181</v>
       </c>
       <c r="E98">
-        <v>313.05572</v>
+        <v>316.31679</v>
       </c>
       <c r="F98">
-        <v>313.06272</v>
+        <v>316.32379</v>
       </c>
       <c r="G98">
         <v>49.6</v>
@@ -9323,28 +9323,28 @@
         <v>47.3</v>
       </c>
       <c r="M98">
-        <v>28.1756448</v>
+        <v>28.4691411</v>
       </c>
       <c r="N98">
-        <v>19.1243552</v>
+        <v>18.8308589</v>
       </c>
       <c r="O98">
-        <v>2.868653280000001</v>
+        <v>2.824628835</v>
       </c>
       <c r="P98">
-        <v>16.25570192</v>
+        <v>16.006230065</v>
       </c>
       <c r="Q98">
-        <v>34.35570192</v>
+        <v>34.10623006500001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.716467450220202</v>
+        <v>2.269453171671592</v>
       </c>
       <c r="T98">
-        <v>20.01416556362535</v>
+        <v>26.63879201575991</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.678754837227363</v>
+        <v>1.661448086328112</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1422885951501478</v>
+        <v>0.1424784922914875</v>
       </c>
       <c r="C99">
-        <v>-23.65036030498186</v>
+        <v>-27.21405812353942</v>
       </c>
       <c r="D99">
-        <v>243.0734296950181</v>
+        <v>242.7708018764606</v>
       </c>
       <c r="E99">
-        <v>316.31679</v>
+        <v>319.57786</v>
       </c>
       <c r="F99">
-        <v>316.32379</v>
+        <v>319.58486</v>
       </c>
       <c r="G99">
         <v>49.6</v>
@@ -9405,28 +9405,28 @@
         <v>47.3</v>
       </c>
       <c r="M99">
-        <v>28.4691411</v>
+        <v>28.7626374</v>
       </c>
       <c r="N99">
-        <v>18.8308589</v>
+        <v>18.5373626</v>
       </c>
       <c r="O99">
-        <v>2.824628835</v>
+        <v>2.78060439</v>
       </c>
       <c r="P99">
-        <v>16.006230065</v>
+        <v>15.75675821</v>
       </c>
       <c r="Q99">
-        <v>34.10623006500001</v>
+        <v>33.85675821</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.269453171671592</v>
+        <v>3.375424614574373</v>
       </c>
       <c r="T99">
-        <v>26.63879201575991</v>
+        <v>39.88804492002902</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.661448086328112</v>
+        <v>1.644494534426805</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1424784922914875</v>
+        <v>0.1426683894328272</v>
       </c>
       <c r="C100">
-        <v>-27.21405812353942</v>
+        <v>-30.77700333234975</v>
       </c>
       <c r="D100">
-        <v>242.7708018764606</v>
+        <v>242.4689266676503</v>
       </c>
       <c r="E100">
-        <v>319.57786</v>
+        <v>322.83893</v>
       </c>
       <c r="F100">
-        <v>319.58486</v>
+        <v>322.84593</v>
       </c>
       <c r="G100">
         <v>49.6</v>
@@ -9487,28 +9487,28 @@
         <v>47.3</v>
       </c>
       <c r="M100">
-        <v>28.7626374</v>
+        <v>29.0561337</v>
       </c>
       <c r="N100">
-        <v>18.5373626</v>
+        <v>18.2438663</v>
       </c>
       <c r="O100">
-        <v>2.78060439</v>
+        <v>2.736579945</v>
       </c>
       <c r="P100">
-        <v>15.75675821</v>
+        <v>15.507286355</v>
       </c>
       <c r="Q100">
-        <v>33.85675821</v>
+        <v>33.60728635500001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.375424614574373</v>
+        <v>6.693338943282718</v>
       </c>
       <c r="T100">
-        <v>39.88804492002902</v>
+        <v>79.63580363283637</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.644494534426805</v>
+        <v>1.627883478523504</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1426683894328272</v>
-      </c>
-      <c r="C101">
-        <v>-30.77700333234975</v>
-      </c>
-      <c r="D101">
-        <v>242.4689266676503</v>
-      </c>
-      <c r="E101">
-        <v>322.83893</v>
-      </c>
-      <c r="F101">
-        <v>322.84593</v>
-      </c>
-      <c r="G101">
-        <v>49.6</v>
-      </c>
-      <c r="H101">
-        <v>326.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="K101">
-        <v>18.1</v>
-      </c>
-      <c r="L101">
-        <v>47.3</v>
-      </c>
-      <c r="M101">
-        <v>29.0561337</v>
-      </c>
-      <c r="N101">
-        <v>18.2438663</v>
-      </c>
-      <c r="O101">
-        <v>2.736579945</v>
-      </c>
-      <c r="P101">
-        <v>15.507286355</v>
-      </c>
-      <c r="Q101">
-        <v>33.60728635500001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.693338943282718</v>
-      </c>
-      <c r="T101">
-        <v>79.63580363283637</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.0765</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.627883478523504</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
